--- a/assets/downloads/uriage-kanri-template.xlsx
+++ b/assets/downloads/uriage-kanri-template.xlsx
@@ -19,12 +19,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0&quot;円&quot;;[Red]-#,##0&quot;円&quot;;-"/>
-    <numFmt numFmtId="166" formatCode="#,##0;[Red]-#,##0;-"/>
-    <numFmt numFmtId="167" formatCode="yyyy/mm"/>
-    <numFmt numFmtId="168" formatCode="0.0%;[Red]-0.0%;-"/>
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot;円&quot;;[Red]-#,##0&quot;円&quot;;-"/>
+    <numFmt numFmtId="167" formatCode="#,##0;[Red]-#,##0;-"/>
+    <numFmt numFmtId="168" formatCode="yyyy/mm"/>
+    <numFmt numFmtId="169" formatCode="0.0%;[Red]-0.0%;-"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -115,45 +116,45 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -914,10 +915,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>2026/10/01</t>
-        </is>
+      <c r="A5" s="8" t="n">
+        <v>46296</v>
       </c>
       <c r="B5" s="9">
         <f>IF($A5="","",TEXT($A5,"aaa"))</f>
@@ -8992,10 +8991,8 @@
           <t>集計を始める月</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>2026/10/01</t>
-        </is>
+      <c r="B4" s="21" t="n">
+        <v>46296</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>

--- a/assets/downloads/uriage-kanri-template.xlsx
+++ b/assets/downloads/uriage-kanri-template.xlsx
@@ -919,7 +919,7 @@
         <v>46296</v>
       </c>
       <c r="B5" s="9">
-        <f>IF($A5="","",TEXT($A5,"aaa"))</f>
+        <f>IF($A5="","",CHOOSE(WEEKDAY($A5),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C5" s="10" t="n">
@@ -955,7 +955,7 @@
     <row r="6">
       <c r="A6" s="8" t="n"/>
       <c r="B6" s="9">
-        <f>IF($A6="","",TEXT($A6,"aaa"))</f>
+        <f>IF($A6="","",CHOOSE(WEEKDAY($A6),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C6" s="10" t="n"/>
@@ -975,7 +975,7 @@
     <row r="7">
       <c r="A7" s="8" t="n"/>
       <c r="B7" s="9">
-        <f>IF($A7="","",TEXT($A7,"aaa"))</f>
+        <f>IF($A7="","",CHOOSE(WEEKDAY($A7),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C7" s="10" t="n"/>
@@ -995,7 +995,7 @@
     <row r="8">
       <c r="A8" s="8" t="n"/>
       <c r="B8" s="9">
-        <f>IF($A8="","",TEXT($A8,"aaa"))</f>
+        <f>IF($A8="","",CHOOSE(WEEKDAY($A8),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C8" s="10" t="n"/>
@@ -1015,7 +1015,7 @@
     <row r="9">
       <c r="A9" s="8" t="n"/>
       <c r="B9" s="9">
-        <f>IF($A9="","",TEXT($A9,"aaa"))</f>
+        <f>IF($A9="","",CHOOSE(WEEKDAY($A9),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C9" s="10" t="n"/>
@@ -1035,7 +1035,7 @@
     <row r="10">
       <c r="A10" s="8" t="n"/>
       <c r="B10" s="9">
-        <f>IF($A10="","",TEXT($A10,"aaa"))</f>
+        <f>IF($A10="","",CHOOSE(WEEKDAY($A10),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C10" s="10" t="n"/>
@@ -1055,7 +1055,7 @@
     <row r="11">
       <c r="A11" s="8" t="n"/>
       <c r="B11" s="9">
-        <f>IF($A11="","",TEXT($A11,"aaa"))</f>
+        <f>IF($A11="","",CHOOSE(WEEKDAY($A11),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C11" s="10" t="n"/>
@@ -1075,7 +1075,7 @@
     <row r="12">
       <c r="A12" s="8" t="n"/>
       <c r="B12" s="9">
-        <f>IF($A12="","",TEXT($A12,"aaa"))</f>
+        <f>IF($A12="","",CHOOSE(WEEKDAY($A12),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C12" s="10" t="n"/>
@@ -1095,7 +1095,7 @@
     <row r="13">
       <c r="A13" s="8" t="n"/>
       <c r="B13" s="9">
-        <f>IF($A13="","",TEXT($A13,"aaa"))</f>
+        <f>IF($A13="","",CHOOSE(WEEKDAY($A13),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C13" s="10" t="n"/>
@@ -1115,7 +1115,7 @@
     <row r="14">
       <c r="A14" s="8" t="n"/>
       <c r="B14" s="9">
-        <f>IF($A14="","",TEXT($A14,"aaa"))</f>
+        <f>IF($A14="","",CHOOSE(WEEKDAY($A14),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C14" s="10" t="n"/>
@@ -1135,7 +1135,7 @@
     <row r="15">
       <c r="A15" s="8" t="n"/>
       <c r="B15" s="9">
-        <f>IF($A15="","",TEXT($A15,"aaa"))</f>
+        <f>IF($A15="","",CHOOSE(WEEKDAY($A15),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C15" s="10" t="n"/>
@@ -1155,7 +1155,7 @@
     <row r="16">
       <c r="A16" s="8" t="n"/>
       <c r="B16" s="9">
-        <f>IF($A16="","",TEXT($A16,"aaa"))</f>
+        <f>IF($A16="","",CHOOSE(WEEKDAY($A16),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C16" s="10" t="n"/>
@@ -1175,7 +1175,7 @@
     <row r="17">
       <c r="A17" s="8" t="n"/>
       <c r="B17" s="9">
-        <f>IF($A17="","",TEXT($A17,"aaa"))</f>
+        <f>IF($A17="","",CHOOSE(WEEKDAY($A17),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C17" s="10" t="n"/>
@@ -1195,7 +1195,7 @@
     <row r="18">
       <c r="A18" s="8" t="n"/>
       <c r="B18" s="9">
-        <f>IF($A18="","",TEXT($A18,"aaa"))</f>
+        <f>IF($A18="","",CHOOSE(WEEKDAY($A18),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C18" s="10" t="n"/>
@@ -1215,7 +1215,7 @@
     <row r="19">
       <c r="A19" s="8" t="n"/>
       <c r="B19" s="9">
-        <f>IF($A19="","",TEXT($A19,"aaa"))</f>
+        <f>IF($A19="","",CHOOSE(WEEKDAY($A19),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C19" s="10" t="n"/>
@@ -1235,7 +1235,7 @@
     <row r="20">
       <c r="A20" s="8" t="n"/>
       <c r="B20" s="9">
-        <f>IF($A20="","",TEXT($A20,"aaa"))</f>
+        <f>IF($A20="","",CHOOSE(WEEKDAY($A20),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -1255,7 +1255,7 @@
     <row r="21">
       <c r="A21" s="8" t="n"/>
       <c r="B21" s="9">
-        <f>IF($A21="","",TEXT($A21,"aaa"))</f>
+        <f>IF($A21="","",CHOOSE(WEEKDAY($A21),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C21" s="10" t="n"/>
@@ -1275,7 +1275,7 @@
     <row r="22">
       <c r="A22" s="8" t="n"/>
       <c r="B22" s="9">
-        <f>IF($A22="","",TEXT($A22,"aaa"))</f>
+        <f>IF($A22="","",CHOOSE(WEEKDAY($A22),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C22" s="10" t="n"/>
@@ -1295,7 +1295,7 @@
     <row r="23">
       <c r="A23" s="8" t="n"/>
       <c r="B23" s="9">
-        <f>IF($A23="","",TEXT($A23,"aaa"))</f>
+        <f>IF($A23="","",CHOOSE(WEEKDAY($A23),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C23" s="10" t="n"/>
@@ -1315,7 +1315,7 @@
     <row r="24">
       <c r="A24" s="8" t="n"/>
       <c r="B24" s="9">
-        <f>IF($A24="","",TEXT($A24,"aaa"))</f>
+        <f>IF($A24="","",CHOOSE(WEEKDAY($A24),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C24" s="10" t="n"/>
@@ -1335,7 +1335,7 @@
     <row r="25">
       <c r="A25" s="8" t="n"/>
       <c r="B25" s="9">
-        <f>IF($A25="","",TEXT($A25,"aaa"))</f>
+        <f>IF($A25="","",CHOOSE(WEEKDAY($A25),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C25" s="10" t="n"/>
@@ -1355,7 +1355,7 @@
     <row r="26">
       <c r="A26" s="8" t="n"/>
       <c r="B26" s="9">
-        <f>IF($A26="","",TEXT($A26,"aaa"))</f>
+        <f>IF($A26="","",CHOOSE(WEEKDAY($A26),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C26" s="10" t="n"/>
@@ -1375,7 +1375,7 @@
     <row r="27">
       <c r="A27" s="8" t="n"/>
       <c r="B27" s="9">
-        <f>IF($A27="","",TEXT($A27,"aaa"))</f>
+        <f>IF($A27="","",CHOOSE(WEEKDAY($A27),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C27" s="10" t="n"/>
@@ -1395,7 +1395,7 @@
     <row r="28">
       <c r="A28" s="8" t="n"/>
       <c r="B28" s="9">
-        <f>IF($A28="","",TEXT($A28,"aaa"))</f>
+        <f>IF($A28="","",CHOOSE(WEEKDAY($A28),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C28" s="10" t="n"/>
@@ -1415,7 +1415,7 @@
     <row r="29">
       <c r="A29" s="8" t="n"/>
       <c r="B29" s="9">
-        <f>IF($A29="","",TEXT($A29,"aaa"))</f>
+        <f>IF($A29="","",CHOOSE(WEEKDAY($A29),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C29" s="10" t="n"/>
@@ -1435,7 +1435,7 @@
     <row r="30">
       <c r="A30" s="8" t="n"/>
       <c r="B30" s="9">
-        <f>IF($A30="","",TEXT($A30,"aaa"))</f>
+        <f>IF($A30="","",CHOOSE(WEEKDAY($A30),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C30" s="10" t="n"/>
@@ -1455,7 +1455,7 @@
     <row r="31">
       <c r="A31" s="8" t="n"/>
       <c r="B31" s="9">
-        <f>IF($A31="","",TEXT($A31,"aaa"))</f>
+        <f>IF($A31="","",CHOOSE(WEEKDAY($A31),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C31" s="10" t="n"/>
@@ -1475,7 +1475,7 @@
     <row r="32">
       <c r="A32" s="8" t="n"/>
       <c r="B32" s="9">
-        <f>IF($A32="","",TEXT($A32,"aaa"))</f>
+        <f>IF($A32="","",CHOOSE(WEEKDAY($A32),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C32" s="10" t="n"/>
@@ -1495,7 +1495,7 @@
     <row r="33">
       <c r="A33" s="8" t="n"/>
       <c r="B33" s="9">
-        <f>IF($A33="","",TEXT($A33,"aaa"))</f>
+        <f>IF($A33="","",CHOOSE(WEEKDAY($A33),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C33" s="10" t="n"/>
@@ -1515,7 +1515,7 @@
     <row r="34">
       <c r="A34" s="8" t="n"/>
       <c r="B34" s="9">
-        <f>IF($A34="","",TEXT($A34,"aaa"))</f>
+        <f>IF($A34="","",CHOOSE(WEEKDAY($A34),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C34" s="10" t="n"/>
@@ -1535,7 +1535,7 @@
     <row r="35">
       <c r="A35" s="8" t="n"/>
       <c r="B35" s="9">
-        <f>IF($A35="","",TEXT($A35,"aaa"))</f>
+        <f>IF($A35="","",CHOOSE(WEEKDAY($A35),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C35" s="10" t="n"/>
@@ -1555,7 +1555,7 @@
     <row r="36">
       <c r="A36" s="8" t="n"/>
       <c r="B36" s="9">
-        <f>IF($A36="","",TEXT($A36,"aaa"))</f>
+        <f>IF($A36="","",CHOOSE(WEEKDAY($A36),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C36" s="10" t="n"/>
@@ -1575,7 +1575,7 @@
     <row r="37">
       <c r="A37" s="8" t="n"/>
       <c r="B37" s="9">
-        <f>IF($A37="","",TEXT($A37,"aaa"))</f>
+        <f>IF($A37="","",CHOOSE(WEEKDAY($A37),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C37" s="10" t="n"/>
@@ -1595,7 +1595,7 @@
     <row r="38">
       <c r="A38" s="8" t="n"/>
       <c r="B38" s="9">
-        <f>IF($A38="","",TEXT($A38,"aaa"))</f>
+        <f>IF($A38="","",CHOOSE(WEEKDAY($A38),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C38" s="10" t="n"/>
@@ -1615,7 +1615,7 @@
     <row r="39">
       <c r="A39" s="8" t="n"/>
       <c r="B39" s="9">
-        <f>IF($A39="","",TEXT($A39,"aaa"))</f>
+        <f>IF($A39="","",CHOOSE(WEEKDAY($A39),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C39" s="10" t="n"/>
@@ -1635,7 +1635,7 @@
     <row r="40">
       <c r="A40" s="14" t="n"/>
       <c r="B40" s="15">
-        <f>IF($A40="","",TEXT($A40,"aaa"))</f>
+        <f>IF($A40="","",CHOOSE(WEEKDAY($A40),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C40" s="16" t="n"/>
@@ -1655,7 +1655,7 @@
     <row r="41">
       <c r="A41" s="14" t="n"/>
       <c r="B41" s="15">
-        <f>IF($A41="","",TEXT($A41,"aaa"))</f>
+        <f>IF($A41="","",CHOOSE(WEEKDAY($A41),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C41" s="16" t="n"/>
@@ -1675,7 +1675,7 @@
     <row r="42">
       <c r="A42" s="14" t="n"/>
       <c r="B42" s="15">
-        <f>IF($A42="","",TEXT($A42,"aaa"))</f>
+        <f>IF($A42="","",CHOOSE(WEEKDAY($A42),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C42" s="16" t="n"/>
@@ -1695,7 +1695,7 @@
     <row r="43">
       <c r="A43" s="14" t="n"/>
       <c r="B43" s="15">
-        <f>IF($A43="","",TEXT($A43,"aaa"))</f>
+        <f>IF($A43="","",CHOOSE(WEEKDAY($A43),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C43" s="16" t="n"/>
@@ -1715,7 +1715,7 @@
     <row r="44">
       <c r="A44" s="14" t="n"/>
       <c r="B44" s="15">
-        <f>IF($A44="","",TEXT($A44,"aaa"))</f>
+        <f>IF($A44="","",CHOOSE(WEEKDAY($A44),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C44" s="16" t="n"/>
@@ -1735,7 +1735,7 @@
     <row r="45">
       <c r="A45" s="14" t="n"/>
       <c r="B45" s="15">
-        <f>IF($A45="","",TEXT($A45,"aaa"))</f>
+        <f>IF($A45="","",CHOOSE(WEEKDAY($A45),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C45" s="16" t="n"/>
@@ -1755,7 +1755,7 @@
     <row r="46">
       <c r="A46" s="14" t="n"/>
       <c r="B46" s="15">
-        <f>IF($A46="","",TEXT($A46,"aaa"))</f>
+        <f>IF($A46="","",CHOOSE(WEEKDAY($A46),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C46" s="16" t="n"/>
@@ -1775,7 +1775,7 @@
     <row r="47">
       <c r="A47" s="14" t="n"/>
       <c r="B47" s="15">
-        <f>IF($A47="","",TEXT($A47,"aaa"))</f>
+        <f>IF($A47="","",CHOOSE(WEEKDAY($A47),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C47" s="16" t="n"/>
@@ -1795,7 +1795,7 @@
     <row r="48">
       <c r="A48" s="14" t="n"/>
       <c r="B48" s="15">
-        <f>IF($A48="","",TEXT($A48,"aaa"))</f>
+        <f>IF($A48="","",CHOOSE(WEEKDAY($A48),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C48" s="16" t="n"/>
@@ -1815,7 +1815,7 @@
     <row r="49">
       <c r="A49" s="14" t="n"/>
       <c r="B49" s="15">
-        <f>IF($A49="","",TEXT($A49,"aaa"))</f>
+        <f>IF($A49="","",CHOOSE(WEEKDAY($A49),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C49" s="16" t="n"/>
@@ -1835,7 +1835,7 @@
     <row r="50">
       <c r="A50" s="14" t="n"/>
       <c r="B50" s="15">
-        <f>IF($A50="","",TEXT($A50,"aaa"))</f>
+        <f>IF($A50="","",CHOOSE(WEEKDAY($A50),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C50" s="16" t="n"/>
@@ -1855,7 +1855,7 @@
     <row r="51">
       <c r="A51" s="14" t="n"/>
       <c r="B51" s="15">
-        <f>IF($A51="","",TEXT($A51,"aaa"))</f>
+        <f>IF($A51="","",CHOOSE(WEEKDAY($A51),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C51" s="16" t="n"/>
@@ -1875,7 +1875,7 @@
     <row r="52">
       <c r="A52" s="14" t="n"/>
       <c r="B52" s="15">
-        <f>IF($A52="","",TEXT($A52,"aaa"))</f>
+        <f>IF($A52="","",CHOOSE(WEEKDAY($A52),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C52" s="16" t="n"/>
@@ -1895,7 +1895,7 @@
     <row r="53">
       <c r="A53" s="14" t="n"/>
       <c r="B53" s="15">
-        <f>IF($A53="","",TEXT($A53,"aaa"))</f>
+        <f>IF($A53="","",CHOOSE(WEEKDAY($A53),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C53" s="16" t="n"/>
@@ -1915,7 +1915,7 @@
     <row r="54">
       <c r="A54" s="14" t="n"/>
       <c r="B54" s="15">
-        <f>IF($A54="","",TEXT($A54,"aaa"))</f>
+        <f>IF($A54="","",CHOOSE(WEEKDAY($A54),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C54" s="16" t="n"/>
@@ -1935,7 +1935,7 @@
     <row r="55">
       <c r="A55" s="14" t="n"/>
       <c r="B55" s="15">
-        <f>IF($A55="","",TEXT($A55,"aaa"))</f>
+        <f>IF($A55="","",CHOOSE(WEEKDAY($A55),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C55" s="16" t="n"/>
@@ -1955,7 +1955,7 @@
     <row r="56">
       <c r="A56" s="14" t="n"/>
       <c r="B56" s="15">
-        <f>IF($A56="","",TEXT($A56,"aaa"))</f>
+        <f>IF($A56="","",CHOOSE(WEEKDAY($A56),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C56" s="16" t="n"/>
@@ -1975,7 +1975,7 @@
     <row r="57">
       <c r="A57" s="14" t="n"/>
       <c r="B57" s="15">
-        <f>IF($A57="","",TEXT($A57,"aaa"))</f>
+        <f>IF($A57="","",CHOOSE(WEEKDAY($A57),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C57" s="16" t="n"/>
@@ -1995,7 +1995,7 @@
     <row r="58">
       <c r="A58" s="14" t="n"/>
       <c r="B58" s="15">
-        <f>IF($A58="","",TEXT($A58,"aaa"))</f>
+        <f>IF($A58="","",CHOOSE(WEEKDAY($A58),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C58" s="16" t="n"/>
@@ -2015,7 +2015,7 @@
     <row r="59">
       <c r="A59" s="14" t="n"/>
       <c r="B59" s="15">
-        <f>IF($A59="","",TEXT($A59,"aaa"))</f>
+        <f>IF($A59="","",CHOOSE(WEEKDAY($A59),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C59" s="16" t="n"/>
@@ -2035,7 +2035,7 @@
     <row r="60">
       <c r="A60" s="14" t="n"/>
       <c r="B60" s="15">
-        <f>IF($A60="","",TEXT($A60,"aaa"))</f>
+        <f>IF($A60="","",CHOOSE(WEEKDAY($A60),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C60" s="16" t="n"/>
@@ -2055,7 +2055,7 @@
     <row r="61">
       <c r="A61" s="14" t="n"/>
       <c r="B61" s="15">
-        <f>IF($A61="","",TEXT($A61,"aaa"))</f>
+        <f>IF($A61="","",CHOOSE(WEEKDAY($A61),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C61" s="16" t="n"/>
@@ -2075,7 +2075,7 @@
     <row r="62">
       <c r="A62" s="14" t="n"/>
       <c r="B62" s="15">
-        <f>IF($A62="","",TEXT($A62,"aaa"))</f>
+        <f>IF($A62="","",CHOOSE(WEEKDAY($A62),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C62" s="16" t="n"/>
@@ -2095,7 +2095,7 @@
     <row r="63">
       <c r="A63" s="14" t="n"/>
       <c r="B63" s="15">
-        <f>IF($A63="","",TEXT($A63,"aaa"))</f>
+        <f>IF($A63="","",CHOOSE(WEEKDAY($A63),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C63" s="16" t="n"/>
@@ -2115,7 +2115,7 @@
     <row r="64">
       <c r="A64" s="14" t="n"/>
       <c r="B64" s="15">
-        <f>IF($A64="","",TEXT($A64,"aaa"))</f>
+        <f>IF($A64="","",CHOOSE(WEEKDAY($A64),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C64" s="16" t="n"/>
@@ -2135,7 +2135,7 @@
     <row r="65">
       <c r="A65" s="14" t="n"/>
       <c r="B65" s="15">
-        <f>IF($A65="","",TEXT($A65,"aaa"))</f>
+        <f>IF($A65="","",CHOOSE(WEEKDAY($A65),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C65" s="16" t="n"/>
@@ -2155,7 +2155,7 @@
     <row r="66">
       <c r="A66" s="14" t="n"/>
       <c r="B66" s="15">
-        <f>IF($A66="","",TEXT($A66,"aaa"))</f>
+        <f>IF($A66="","",CHOOSE(WEEKDAY($A66),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C66" s="16" t="n"/>
@@ -2175,7 +2175,7 @@
     <row r="67">
       <c r="A67" s="14" t="n"/>
       <c r="B67" s="15">
-        <f>IF($A67="","",TEXT($A67,"aaa"))</f>
+        <f>IF($A67="","",CHOOSE(WEEKDAY($A67),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C67" s="16" t="n"/>
@@ -2195,7 +2195,7 @@
     <row r="68">
       <c r="A68" s="14" t="n"/>
       <c r="B68" s="15">
-        <f>IF($A68="","",TEXT($A68,"aaa"))</f>
+        <f>IF($A68="","",CHOOSE(WEEKDAY($A68),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C68" s="16" t="n"/>
@@ -2215,7 +2215,7 @@
     <row r="69">
       <c r="A69" s="14" t="n"/>
       <c r="B69" s="15">
-        <f>IF($A69="","",TEXT($A69,"aaa"))</f>
+        <f>IF($A69="","",CHOOSE(WEEKDAY($A69),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C69" s="16" t="n"/>
@@ -2235,7 +2235,7 @@
     <row r="70">
       <c r="A70" s="14" t="n"/>
       <c r="B70" s="15">
-        <f>IF($A70="","",TEXT($A70,"aaa"))</f>
+        <f>IF($A70="","",CHOOSE(WEEKDAY($A70),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C70" s="16" t="n"/>
@@ -2255,7 +2255,7 @@
     <row r="71">
       <c r="A71" s="14" t="n"/>
       <c r="B71" s="15">
-        <f>IF($A71="","",TEXT($A71,"aaa"))</f>
+        <f>IF($A71="","",CHOOSE(WEEKDAY($A71),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C71" s="16" t="n"/>
@@ -2275,7 +2275,7 @@
     <row r="72">
       <c r="A72" s="14" t="n"/>
       <c r="B72" s="15">
-        <f>IF($A72="","",TEXT($A72,"aaa"))</f>
+        <f>IF($A72="","",CHOOSE(WEEKDAY($A72),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C72" s="16" t="n"/>
@@ -2295,7 +2295,7 @@
     <row r="73">
       <c r="A73" s="14" t="n"/>
       <c r="B73" s="15">
-        <f>IF($A73="","",TEXT($A73,"aaa"))</f>
+        <f>IF($A73="","",CHOOSE(WEEKDAY($A73),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C73" s="16" t="n"/>
@@ -2315,7 +2315,7 @@
     <row r="74">
       <c r="A74" s="14" t="n"/>
       <c r="B74" s="15">
-        <f>IF($A74="","",TEXT($A74,"aaa"))</f>
+        <f>IF($A74="","",CHOOSE(WEEKDAY($A74),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C74" s="16" t="n"/>
@@ -2335,7 +2335,7 @@
     <row r="75">
       <c r="A75" s="14" t="n"/>
       <c r="B75" s="15">
-        <f>IF($A75="","",TEXT($A75,"aaa"))</f>
+        <f>IF($A75="","",CHOOSE(WEEKDAY($A75),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C75" s="16" t="n"/>
@@ -2355,7 +2355,7 @@
     <row r="76">
       <c r="A76" s="14" t="n"/>
       <c r="B76" s="15">
-        <f>IF($A76="","",TEXT($A76,"aaa"))</f>
+        <f>IF($A76="","",CHOOSE(WEEKDAY($A76),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C76" s="16" t="n"/>
@@ -2375,7 +2375,7 @@
     <row r="77">
       <c r="A77" s="14" t="n"/>
       <c r="B77" s="15">
-        <f>IF($A77="","",TEXT($A77,"aaa"))</f>
+        <f>IF($A77="","",CHOOSE(WEEKDAY($A77),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C77" s="16" t="n"/>
@@ -2395,7 +2395,7 @@
     <row r="78">
       <c r="A78" s="14" t="n"/>
       <c r="B78" s="15">
-        <f>IF($A78="","",TEXT($A78,"aaa"))</f>
+        <f>IF($A78="","",CHOOSE(WEEKDAY($A78),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C78" s="16" t="n"/>
@@ -2415,7 +2415,7 @@
     <row r="79">
       <c r="A79" s="14" t="n"/>
       <c r="B79" s="15">
-        <f>IF($A79="","",TEXT($A79,"aaa"))</f>
+        <f>IF($A79="","",CHOOSE(WEEKDAY($A79),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C79" s="16" t="n"/>
@@ -2435,7 +2435,7 @@
     <row r="80">
       <c r="A80" s="14" t="n"/>
       <c r="B80" s="15">
-        <f>IF($A80="","",TEXT($A80,"aaa"))</f>
+        <f>IF($A80="","",CHOOSE(WEEKDAY($A80),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C80" s="16" t="n"/>
@@ -2455,7 +2455,7 @@
     <row r="81">
       <c r="A81" s="14" t="n"/>
       <c r="B81" s="15">
-        <f>IF($A81="","",TEXT($A81,"aaa"))</f>
+        <f>IF($A81="","",CHOOSE(WEEKDAY($A81),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C81" s="16" t="n"/>
@@ -2475,7 +2475,7 @@
     <row r="82">
       <c r="A82" s="14" t="n"/>
       <c r="B82" s="15">
-        <f>IF($A82="","",TEXT($A82,"aaa"))</f>
+        <f>IF($A82="","",CHOOSE(WEEKDAY($A82),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C82" s="16" t="n"/>
@@ -2495,7 +2495,7 @@
     <row r="83">
       <c r="A83" s="14" t="n"/>
       <c r="B83" s="15">
-        <f>IF($A83="","",TEXT($A83,"aaa"))</f>
+        <f>IF($A83="","",CHOOSE(WEEKDAY($A83),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C83" s="16" t="n"/>
@@ -2515,7 +2515,7 @@
     <row r="84">
       <c r="A84" s="14" t="n"/>
       <c r="B84" s="15">
-        <f>IF($A84="","",TEXT($A84,"aaa"))</f>
+        <f>IF($A84="","",CHOOSE(WEEKDAY($A84),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C84" s="16" t="n"/>
@@ -2535,7 +2535,7 @@
     <row r="85">
       <c r="A85" s="14" t="n"/>
       <c r="B85" s="15">
-        <f>IF($A85="","",TEXT($A85,"aaa"))</f>
+        <f>IF($A85="","",CHOOSE(WEEKDAY($A85),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C85" s="16" t="n"/>
@@ -2555,7 +2555,7 @@
     <row r="86">
       <c r="A86" s="14" t="n"/>
       <c r="B86" s="15">
-        <f>IF($A86="","",TEXT($A86,"aaa"))</f>
+        <f>IF($A86="","",CHOOSE(WEEKDAY($A86),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C86" s="16" t="n"/>
@@ -2575,7 +2575,7 @@
     <row r="87">
       <c r="A87" s="14" t="n"/>
       <c r="B87" s="15">
-        <f>IF($A87="","",TEXT($A87,"aaa"))</f>
+        <f>IF($A87="","",CHOOSE(WEEKDAY($A87),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C87" s="16" t="n"/>
@@ -2595,7 +2595,7 @@
     <row r="88">
       <c r="A88" s="14" t="n"/>
       <c r="B88" s="15">
-        <f>IF($A88="","",TEXT($A88,"aaa"))</f>
+        <f>IF($A88="","",CHOOSE(WEEKDAY($A88),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C88" s="16" t="n"/>
@@ -2615,7 +2615,7 @@
     <row r="89">
       <c r="A89" s="14" t="n"/>
       <c r="B89" s="15">
-        <f>IF($A89="","",TEXT($A89,"aaa"))</f>
+        <f>IF($A89="","",CHOOSE(WEEKDAY($A89),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C89" s="16" t="n"/>
@@ -2635,7 +2635,7 @@
     <row r="90">
       <c r="A90" s="14" t="n"/>
       <c r="B90" s="15">
-        <f>IF($A90="","",TEXT($A90,"aaa"))</f>
+        <f>IF($A90="","",CHOOSE(WEEKDAY($A90),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C90" s="16" t="n"/>
@@ -2655,7 +2655,7 @@
     <row r="91">
       <c r="A91" s="14" t="n"/>
       <c r="B91" s="15">
-        <f>IF($A91="","",TEXT($A91,"aaa"))</f>
+        <f>IF($A91="","",CHOOSE(WEEKDAY($A91),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C91" s="16" t="n"/>
@@ -2675,7 +2675,7 @@
     <row r="92">
       <c r="A92" s="14" t="n"/>
       <c r="B92" s="15">
-        <f>IF($A92="","",TEXT($A92,"aaa"))</f>
+        <f>IF($A92="","",CHOOSE(WEEKDAY($A92),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C92" s="16" t="n"/>
@@ -2695,7 +2695,7 @@
     <row r="93">
       <c r="A93" s="14" t="n"/>
       <c r="B93" s="15">
-        <f>IF($A93="","",TEXT($A93,"aaa"))</f>
+        <f>IF($A93="","",CHOOSE(WEEKDAY($A93),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C93" s="16" t="n"/>
@@ -2715,7 +2715,7 @@
     <row r="94">
       <c r="A94" s="14" t="n"/>
       <c r="B94" s="15">
-        <f>IF($A94="","",TEXT($A94,"aaa"))</f>
+        <f>IF($A94="","",CHOOSE(WEEKDAY($A94),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C94" s="16" t="n"/>
@@ -2735,7 +2735,7 @@
     <row r="95">
       <c r="A95" s="14" t="n"/>
       <c r="B95" s="15">
-        <f>IF($A95="","",TEXT($A95,"aaa"))</f>
+        <f>IF($A95="","",CHOOSE(WEEKDAY($A95),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C95" s="16" t="n"/>
@@ -2755,7 +2755,7 @@
     <row r="96">
       <c r="A96" s="14" t="n"/>
       <c r="B96" s="15">
-        <f>IF($A96="","",TEXT($A96,"aaa"))</f>
+        <f>IF($A96="","",CHOOSE(WEEKDAY($A96),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C96" s="16" t="n"/>
@@ -2775,7 +2775,7 @@
     <row r="97">
       <c r="A97" s="14" t="n"/>
       <c r="B97" s="15">
-        <f>IF($A97="","",TEXT($A97,"aaa"))</f>
+        <f>IF($A97="","",CHOOSE(WEEKDAY($A97),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C97" s="16" t="n"/>
@@ -2795,7 +2795,7 @@
     <row r="98">
       <c r="A98" s="14" t="n"/>
       <c r="B98" s="15">
-        <f>IF($A98="","",TEXT($A98,"aaa"))</f>
+        <f>IF($A98="","",CHOOSE(WEEKDAY($A98),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C98" s="16" t="n"/>
@@ -2815,7 +2815,7 @@
     <row r="99">
       <c r="A99" s="14" t="n"/>
       <c r="B99" s="15">
-        <f>IF($A99="","",TEXT($A99,"aaa"))</f>
+        <f>IF($A99="","",CHOOSE(WEEKDAY($A99),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C99" s="16" t="n"/>
@@ -2835,7 +2835,7 @@
     <row r="100">
       <c r="A100" s="14" t="n"/>
       <c r="B100" s="15">
-        <f>IF($A100="","",TEXT($A100,"aaa"))</f>
+        <f>IF($A100="","",CHOOSE(WEEKDAY($A100),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C100" s="16" t="n"/>
@@ -2855,7 +2855,7 @@
     <row r="101">
       <c r="A101" s="14" t="n"/>
       <c r="B101" s="15">
-        <f>IF($A101="","",TEXT($A101,"aaa"))</f>
+        <f>IF($A101="","",CHOOSE(WEEKDAY($A101),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C101" s="16" t="n"/>
@@ -2875,7 +2875,7 @@
     <row r="102">
       <c r="A102" s="14" t="n"/>
       <c r="B102" s="15">
-        <f>IF($A102="","",TEXT($A102,"aaa"))</f>
+        <f>IF($A102="","",CHOOSE(WEEKDAY($A102),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C102" s="16" t="n"/>
@@ -2895,7 +2895,7 @@
     <row r="103">
       <c r="A103" s="14" t="n"/>
       <c r="B103" s="15">
-        <f>IF($A103="","",TEXT($A103,"aaa"))</f>
+        <f>IF($A103="","",CHOOSE(WEEKDAY($A103),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C103" s="16" t="n"/>
@@ -2915,7 +2915,7 @@
     <row r="104">
       <c r="A104" s="14" t="n"/>
       <c r="B104" s="15">
-        <f>IF($A104="","",TEXT($A104,"aaa"))</f>
+        <f>IF($A104="","",CHOOSE(WEEKDAY($A104),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C104" s="16" t="n"/>
@@ -2935,7 +2935,7 @@
     <row r="105">
       <c r="A105" s="14" t="n"/>
       <c r="B105" s="15">
-        <f>IF($A105="","",TEXT($A105,"aaa"))</f>
+        <f>IF($A105="","",CHOOSE(WEEKDAY($A105),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C105" s="16" t="n"/>
@@ -2955,7 +2955,7 @@
     <row r="106">
       <c r="A106" s="14" t="n"/>
       <c r="B106" s="15">
-        <f>IF($A106="","",TEXT($A106,"aaa"))</f>
+        <f>IF($A106="","",CHOOSE(WEEKDAY($A106),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C106" s="16" t="n"/>
@@ -2975,7 +2975,7 @@
     <row r="107">
       <c r="A107" s="14" t="n"/>
       <c r="B107" s="15">
-        <f>IF($A107="","",TEXT($A107,"aaa"))</f>
+        <f>IF($A107="","",CHOOSE(WEEKDAY($A107),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C107" s="16" t="n"/>
@@ -2995,7 +2995,7 @@
     <row r="108">
       <c r="A108" s="14" t="n"/>
       <c r="B108" s="15">
-        <f>IF($A108="","",TEXT($A108,"aaa"))</f>
+        <f>IF($A108="","",CHOOSE(WEEKDAY($A108),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C108" s="16" t="n"/>
@@ -3015,7 +3015,7 @@
     <row r="109">
       <c r="A109" s="14" t="n"/>
       <c r="B109" s="15">
-        <f>IF($A109="","",TEXT($A109,"aaa"))</f>
+        <f>IF($A109="","",CHOOSE(WEEKDAY($A109),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C109" s="16" t="n"/>
@@ -3035,7 +3035,7 @@
     <row r="110">
       <c r="A110" s="14" t="n"/>
       <c r="B110" s="15">
-        <f>IF($A110="","",TEXT($A110,"aaa"))</f>
+        <f>IF($A110="","",CHOOSE(WEEKDAY($A110),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C110" s="16" t="n"/>
@@ -3055,7 +3055,7 @@
     <row r="111">
       <c r="A111" s="14" t="n"/>
       <c r="B111" s="15">
-        <f>IF($A111="","",TEXT($A111,"aaa"))</f>
+        <f>IF($A111="","",CHOOSE(WEEKDAY($A111),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C111" s="16" t="n"/>
@@ -3075,7 +3075,7 @@
     <row r="112">
       <c r="A112" s="14" t="n"/>
       <c r="B112" s="15">
-        <f>IF($A112="","",TEXT($A112,"aaa"))</f>
+        <f>IF($A112="","",CHOOSE(WEEKDAY($A112),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C112" s="16" t="n"/>
@@ -3095,7 +3095,7 @@
     <row r="113">
       <c r="A113" s="14" t="n"/>
       <c r="B113" s="15">
-        <f>IF($A113="","",TEXT($A113,"aaa"))</f>
+        <f>IF($A113="","",CHOOSE(WEEKDAY($A113),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C113" s="16" t="n"/>
@@ -3115,7 +3115,7 @@
     <row r="114">
       <c r="A114" s="14" t="n"/>
       <c r="B114" s="15">
-        <f>IF($A114="","",TEXT($A114,"aaa"))</f>
+        <f>IF($A114="","",CHOOSE(WEEKDAY($A114),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C114" s="16" t="n"/>
@@ -3135,7 +3135,7 @@
     <row r="115">
       <c r="A115" s="14" t="n"/>
       <c r="B115" s="15">
-        <f>IF($A115="","",TEXT($A115,"aaa"))</f>
+        <f>IF($A115="","",CHOOSE(WEEKDAY($A115),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C115" s="16" t="n"/>
@@ -3155,7 +3155,7 @@
     <row r="116">
       <c r="A116" s="14" t="n"/>
       <c r="B116" s="15">
-        <f>IF($A116="","",TEXT($A116,"aaa"))</f>
+        <f>IF($A116="","",CHOOSE(WEEKDAY($A116),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C116" s="16" t="n"/>
@@ -3175,7 +3175,7 @@
     <row r="117">
       <c r="A117" s="14" t="n"/>
       <c r="B117" s="15">
-        <f>IF($A117="","",TEXT($A117,"aaa"))</f>
+        <f>IF($A117="","",CHOOSE(WEEKDAY($A117),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C117" s="16" t="n"/>
@@ -3195,7 +3195,7 @@
     <row r="118">
       <c r="A118" s="14" t="n"/>
       <c r="B118" s="15">
-        <f>IF($A118="","",TEXT($A118,"aaa"))</f>
+        <f>IF($A118="","",CHOOSE(WEEKDAY($A118),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C118" s="16" t="n"/>
@@ -3215,7 +3215,7 @@
     <row r="119">
       <c r="A119" s="14" t="n"/>
       <c r="B119" s="15">
-        <f>IF($A119="","",TEXT($A119,"aaa"))</f>
+        <f>IF($A119="","",CHOOSE(WEEKDAY($A119),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C119" s="16" t="n"/>
@@ -3235,7 +3235,7 @@
     <row r="120">
       <c r="A120" s="14" t="n"/>
       <c r="B120" s="15">
-        <f>IF($A120="","",TEXT($A120,"aaa"))</f>
+        <f>IF($A120="","",CHOOSE(WEEKDAY($A120),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C120" s="16" t="n"/>
@@ -3255,7 +3255,7 @@
     <row r="121">
       <c r="A121" s="14" t="n"/>
       <c r="B121" s="15">
-        <f>IF($A121="","",TEXT($A121,"aaa"))</f>
+        <f>IF($A121="","",CHOOSE(WEEKDAY($A121),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C121" s="16" t="n"/>
@@ -3275,7 +3275,7 @@
     <row r="122">
       <c r="A122" s="14" t="n"/>
       <c r="B122" s="15">
-        <f>IF($A122="","",TEXT($A122,"aaa"))</f>
+        <f>IF($A122="","",CHOOSE(WEEKDAY($A122),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C122" s="16" t="n"/>
@@ -3295,7 +3295,7 @@
     <row r="123">
       <c r="A123" s="14" t="n"/>
       <c r="B123" s="15">
-        <f>IF($A123="","",TEXT($A123,"aaa"))</f>
+        <f>IF($A123="","",CHOOSE(WEEKDAY($A123),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C123" s="16" t="n"/>
@@ -3315,7 +3315,7 @@
     <row r="124">
       <c r="A124" s="14" t="n"/>
       <c r="B124" s="15">
-        <f>IF($A124="","",TEXT($A124,"aaa"))</f>
+        <f>IF($A124="","",CHOOSE(WEEKDAY($A124),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C124" s="16" t="n"/>
@@ -3335,7 +3335,7 @@
     <row r="125">
       <c r="A125" s="14" t="n"/>
       <c r="B125" s="15">
-        <f>IF($A125="","",TEXT($A125,"aaa"))</f>
+        <f>IF($A125="","",CHOOSE(WEEKDAY($A125),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C125" s="16" t="n"/>
@@ -3355,7 +3355,7 @@
     <row r="126">
       <c r="A126" s="14" t="n"/>
       <c r="B126" s="15">
-        <f>IF($A126="","",TEXT($A126,"aaa"))</f>
+        <f>IF($A126="","",CHOOSE(WEEKDAY($A126),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C126" s="16" t="n"/>
@@ -3375,7 +3375,7 @@
     <row r="127">
       <c r="A127" s="14" t="n"/>
       <c r="B127" s="15">
-        <f>IF($A127="","",TEXT($A127,"aaa"))</f>
+        <f>IF($A127="","",CHOOSE(WEEKDAY($A127),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C127" s="16" t="n"/>
@@ -3395,7 +3395,7 @@
     <row r="128">
       <c r="A128" s="14" t="n"/>
       <c r="B128" s="15">
-        <f>IF($A128="","",TEXT($A128,"aaa"))</f>
+        <f>IF($A128="","",CHOOSE(WEEKDAY($A128),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C128" s="16" t="n"/>
@@ -3415,7 +3415,7 @@
     <row r="129">
       <c r="A129" s="14" t="n"/>
       <c r="B129" s="15">
-        <f>IF($A129="","",TEXT($A129,"aaa"))</f>
+        <f>IF($A129="","",CHOOSE(WEEKDAY($A129),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C129" s="16" t="n"/>
@@ -3435,7 +3435,7 @@
     <row r="130">
       <c r="A130" s="14" t="n"/>
       <c r="B130" s="15">
-        <f>IF($A130="","",TEXT($A130,"aaa"))</f>
+        <f>IF($A130="","",CHOOSE(WEEKDAY($A130),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C130" s="16" t="n"/>
@@ -3455,7 +3455,7 @@
     <row r="131">
       <c r="A131" s="14" t="n"/>
       <c r="B131" s="15">
-        <f>IF($A131="","",TEXT($A131,"aaa"))</f>
+        <f>IF($A131="","",CHOOSE(WEEKDAY($A131),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C131" s="16" t="n"/>
@@ -3475,7 +3475,7 @@
     <row r="132">
       <c r="A132" s="14" t="n"/>
       <c r="B132" s="15">
-        <f>IF($A132="","",TEXT($A132,"aaa"))</f>
+        <f>IF($A132="","",CHOOSE(WEEKDAY($A132),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C132" s="16" t="n"/>
@@ -3495,7 +3495,7 @@
     <row r="133">
       <c r="A133" s="14" t="n"/>
       <c r="B133" s="15">
-        <f>IF($A133="","",TEXT($A133,"aaa"))</f>
+        <f>IF($A133="","",CHOOSE(WEEKDAY($A133),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C133" s="16" t="n"/>
@@ -3515,7 +3515,7 @@
     <row r="134">
       <c r="A134" s="14" t="n"/>
       <c r="B134" s="15">
-        <f>IF($A134="","",TEXT($A134,"aaa"))</f>
+        <f>IF($A134="","",CHOOSE(WEEKDAY($A134),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C134" s="16" t="n"/>
@@ -3535,7 +3535,7 @@
     <row r="135">
       <c r="A135" s="14" t="n"/>
       <c r="B135" s="15">
-        <f>IF($A135="","",TEXT($A135,"aaa"))</f>
+        <f>IF($A135="","",CHOOSE(WEEKDAY($A135),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C135" s="16" t="n"/>
@@ -3555,7 +3555,7 @@
     <row r="136">
       <c r="A136" s="14" t="n"/>
       <c r="B136" s="15">
-        <f>IF($A136="","",TEXT($A136,"aaa"))</f>
+        <f>IF($A136="","",CHOOSE(WEEKDAY($A136),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C136" s="16" t="n"/>
@@ -3575,7 +3575,7 @@
     <row r="137">
       <c r="A137" s="14" t="n"/>
       <c r="B137" s="15">
-        <f>IF($A137="","",TEXT($A137,"aaa"))</f>
+        <f>IF($A137="","",CHOOSE(WEEKDAY($A137),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C137" s="16" t="n"/>
@@ -3595,7 +3595,7 @@
     <row r="138">
       <c r="A138" s="14" t="n"/>
       <c r="B138" s="15">
-        <f>IF($A138="","",TEXT($A138,"aaa"))</f>
+        <f>IF($A138="","",CHOOSE(WEEKDAY($A138),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C138" s="16" t="n"/>
@@ -3615,7 +3615,7 @@
     <row r="139">
       <c r="A139" s="14" t="n"/>
       <c r="B139" s="15">
-        <f>IF($A139="","",TEXT($A139,"aaa"))</f>
+        <f>IF($A139="","",CHOOSE(WEEKDAY($A139),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C139" s="16" t="n"/>
@@ -3635,7 +3635,7 @@
     <row r="140">
       <c r="A140" s="14" t="n"/>
       <c r="B140" s="15">
-        <f>IF($A140="","",TEXT($A140,"aaa"))</f>
+        <f>IF($A140="","",CHOOSE(WEEKDAY($A140),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C140" s="16" t="n"/>
@@ -3655,7 +3655,7 @@
     <row r="141">
       <c r="A141" s="14" t="n"/>
       <c r="B141" s="15">
-        <f>IF($A141="","",TEXT($A141,"aaa"))</f>
+        <f>IF($A141="","",CHOOSE(WEEKDAY($A141),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C141" s="16" t="n"/>
@@ -3675,7 +3675,7 @@
     <row r="142">
       <c r="A142" s="14" t="n"/>
       <c r="B142" s="15">
-        <f>IF($A142="","",TEXT($A142,"aaa"))</f>
+        <f>IF($A142="","",CHOOSE(WEEKDAY($A142),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C142" s="16" t="n"/>
@@ -3695,7 +3695,7 @@
     <row r="143">
       <c r="A143" s="14" t="n"/>
       <c r="B143" s="15">
-        <f>IF($A143="","",TEXT($A143,"aaa"))</f>
+        <f>IF($A143="","",CHOOSE(WEEKDAY($A143),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C143" s="16" t="n"/>
@@ -3715,7 +3715,7 @@
     <row r="144">
       <c r="A144" s="14" t="n"/>
       <c r="B144" s="15">
-        <f>IF($A144="","",TEXT($A144,"aaa"))</f>
+        <f>IF($A144="","",CHOOSE(WEEKDAY($A144),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C144" s="16" t="n"/>
@@ -3735,7 +3735,7 @@
     <row r="145">
       <c r="A145" s="14" t="n"/>
       <c r="B145" s="15">
-        <f>IF($A145="","",TEXT($A145,"aaa"))</f>
+        <f>IF($A145="","",CHOOSE(WEEKDAY($A145),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C145" s="16" t="n"/>
@@ -3755,7 +3755,7 @@
     <row r="146">
       <c r="A146" s="14" t="n"/>
       <c r="B146" s="15">
-        <f>IF($A146="","",TEXT($A146,"aaa"))</f>
+        <f>IF($A146="","",CHOOSE(WEEKDAY($A146),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C146" s="16" t="n"/>
@@ -3775,7 +3775,7 @@
     <row r="147">
       <c r="A147" s="14" t="n"/>
       <c r="B147" s="15">
-        <f>IF($A147="","",TEXT($A147,"aaa"))</f>
+        <f>IF($A147="","",CHOOSE(WEEKDAY($A147),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C147" s="16" t="n"/>
@@ -3795,7 +3795,7 @@
     <row r="148">
       <c r="A148" s="14" t="n"/>
       <c r="B148" s="15">
-        <f>IF($A148="","",TEXT($A148,"aaa"))</f>
+        <f>IF($A148="","",CHOOSE(WEEKDAY($A148),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C148" s="16" t="n"/>
@@ -3815,7 +3815,7 @@
     <row r="149">
       <c r="A149" s="14" t="n"/>
       <c r="B149" s="15">
-        <f>IF($A149="","",TEXT($A149,"aaa"))</f>
+        <f>IF($A149="","",CHOOSE(WEEKDAY($A149),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C149" s="16" t="n"/>
@@ -3835,7 +3835,7 @@
     <row r="150">
       <c r="A150" s="14" t="n"/>
       <c r="B150" s="15">
-        <f>IF($A150="","",TEXT($A150,"aaa"))</f>
+        <f>IF($A150="","",CHOOSE(WEEKDAY($A150),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C150" s="16" t="n"/>
@@ -3855,7 +3855,7 @@
     <row r="151">
       <c r="A151" s="14" t="n"/>
       <c r="B151" s="15">
-        <f>IF($A151="","",TEXT($A151,"aaa"))</f>
+        <f>IF($A151="","",CHOOSE(WEEKDAY($A151),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C151" s="16" t="n"/>
@@ -3875,7 +3875,7 @@
     <row r="152">
       <c r="A152" s="14" t="n"/>
       <c r="B152" s="15">
-        <f>IF($A152="","",TEXT($A152,"aaa"))</f>
+        <f>IF($A152="","",CHOOSE(WEEKDAY($A152),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C152" s="16" t="n"/>
@@ -3895,7 +3895,7 @@
     <row r="153">
       <c r="A153" s="14" t="n"/>
       <c r="B153" s="15">
-        <f>IF($A153="","",TEXT($A153,"aaa"))</f>
+        <f>IF($A153="","",CHOOSE(WEEKDAY($A153),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C153" s="16" t="n"/>
@@ -3915,7 +3915,7 @@
     <row r="154">
       <c r="A154" s="14" t="n"/>
       <c r="B154" s="15">
-        <f>IF($A154="","",TEXT($A154,"aaa"))</f>
+        <f>IF($A154="","",CHOOSE(WEEKDAY($A154),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C154" s="16" t="n"/>
@@ -3935,7 +3935,7 @@
     <row r="155">
       <c r="A155" s="14" t="n"/>
       <c r="B155" s="15">
-        <f>IF($A155="","",TEXT($A155,"aaa"))</f>
+        <f>IF($A155="","",CHOOSE(WEEKDAY($A155),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C155" s="16" t="n"/>
@@ -3955,7 +3955,7 @@
     <row r="156">
       <c r="A156" s="14" t="n"/>
       <c r="B156" s="15">
-        <f>IF($A156="","",TEXT($A156,"aaa"))</f>
+        <f>IF($A156="","",CHOOSE(WEEKDAY($A156),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C156" s="16" t="n"/>
@@ -3975,7 +3975,7 @@
     <row r="157">
       <c r="A157" s="14" t="n"/>
       <c r="B157" s="15">
-        <f>IF($A157="","",TEXT($A157,"aaa"))</f>
+        <f>IF($A157="","",CHOOSE(WEEKDAY($A157),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C157" s="16" t="n"/>
@@ -3995,7 +3995,7 @@
     <row r="158">
       <c r="A158" s="14" t="n"/>
       <c r="B158" s="15">
-        <f>IF($A158="","",TEXT($A158,"aaa"))</f>
+        <f>IF($A158="","",CHOOSE(WEEKDAY($A158),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C158" s="16" t="n"/>
@@ -4015,7 +4015,7 @@
     <row r="159">
       <c r="A159" s="14" t="n"/>
       <c r="B159" s="15">
-        <f>IF($A159="","",TEXT($A159,"aaa"))</f>
+        <f>IF($A159="","",CHOOSE(WEEKDAY($A159),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C159" s="16" t="n"/>
@@ -4035,7 +4035,7 @@
     <row r="160">
       <c r="A160" s="14" t="n"/>
       <c r="B160" s="15">
-        <f>IF($A160="","",TEXT($A160,"aaa"))</f>
+        <f>IF($A160="","",CHOOSE(WEEKDAY($A160),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C160" s="16" t="n"/>
@@ -4055,7 +4055,7 @@
     <row r="161">
       <c r="A161" s="14" t="n"/>
       <c r="B161" s="15">
-        <f>IF($A161="","",TEXT($A161,"aaa"))</f>
+        <f>IF($A161="","",CHOOSE(WEEKDAY($A161),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C161" s="16" t="n"/>
@@ -4075,7 +4075,7 @@
     <row r="162">
       <c r="A162" s="14" t="n"/>
       <c r="B162" s="15">
-        <f>IF($A162="","",TEXT($A162,"aaa"))</f>
+        <f>IF($A162="","",CHOOSE(WEEKDAY($A162),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C162" s="16" t="n"/>
@@ -4095,7 +4095,7 @@
     <row r="163">
       <c r="A163" s="14" t="n"/>
       <c r="B163" s="15">
-        <f>IF($A163="","",TEXT($A163,"aaa"))</f>
+        <f>IF($A163="","",CHOOSE(WEEKDAY($A163),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C163" s="16" t="n"/>
@@ -4115,7 +4115,7 @@
     <row r="164">
       <c r="A164" s="14" t="n"/>
       <c r="B164" s="15">
-        <f>IF($A164="","",TEXT($A164,"aaa"))</f>
+        <f>IF($A164="","",CHOOSE(WEEKDAY($A164),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C164" s="16" t="n"/>
@@ -4135,7 +4135,7 @@
     <row r="165">
       <c r="A165" s="14" t="n"/>
       <c r="B165" s="15">
-        <f>IF($A165="","",TEXT($A165,"aaa"))</f>
+        <f>IF($A165="","",CHOOSE(WEEKDAY($A165),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C165" s="16" t="n"/>
@@ -4155,7 +4155,7 @@
     <row r="166">
       <c r="A166" s="14" t="n"/>
       <c r="B166" s="15">
-        <f>IF($A166="","",TEXT($A166,"aaa"))</f>
+        <f>IF($A166="","",CHOOSE(WEEKDAY($A166),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C166" s="16" t="n"/>
@@ -4175,7 +4175,7 @@
     <row r="167">
       <c r="A167" s="14" t="n"/>
       <c r="B167" s="15">
-        <f>IF($A167="","",TEXT($A167,"aaa"))</f>
+        <f>IF($A167="","",CHOOSE(WEEKDAY($A167),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C167" s="16" t="n"/>
@@ -4195,7 +4195,7 @@
     <row r="168">
       <c r="A168" s="14" t="n"/>
       <c r="B168" s="15">
-        <f>IF($A168="","",TEXT($A168,"aaa"))</f>
+        <f>IF($A168="","",CHOOSE(WEEKDAY($A168),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C168" s="16" t="n"/>
@@ -4215,7 +4215,7 @@
     <row r="169">
       <c r="A169" s="14" t="n"/>
       <c r="B169" s="15">
-        <f>IF($A169="","",TEXT($A169,"aaa"))</f>
+        <f>IF($A169="","",CHOOSE(WEEKDAY($A169),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C169" s="16" t="n"/>
@@ -4235,7 +4235,7 @@
     <row r="170">
       <c r="A170" s="14" t="n"/>
       <c r="B170" s="15">
-        <f>IF($A170="","",TEXT($A170,"aaa"))</f>
+        <f>IF($A170="","",CHOOSE(WEEKDAY($A170),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C170" s="16" t="n"/>
@@ -4255,7 +4255,7 @@
     <row r="171">
       <c r="A171" s="14" t="n"/>
       <c r="B171" s="15">
-        <f>IF($A171="","",TEXT($A171,"aaa"))</f>
+        <f>IF($A171="","",CHOOSE(WEEKDAY($A171),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C171" s="16" t="n"/>
@@ -4275,7 +4275,7 @@
     <row r="172">
       <c r="A172" s="14" t="n"/>
       <c r="B172" s="15">
-        <f>IF($A172="","",TEXT($A172,"aaa"))</f>
+        <f>IF($A172="","",CHOOSE(WEEKDAY($A172),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C172" s="16" t="n"/>
@@ -4295,7 +4295,7 @@
     <row r="173">
       <c r="A173" s="14" t="n"/>
       <c r="B173" s="15">
-        <f>IF($A173="","",TEXT($A173,"aaa"))</f>
+        <f>IF($A173="","",CHOOSE(WEEKDAY($A173),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C173" s="16" t="n"/>
@@ -4315,7 +4315,7 @@
     <row r="174">
       <c r="A174" s="14" t="n"/>
       <c r="B174" s="15">
-        <f>IF($A174="","",TEXT($A174,"aaa"))</f>
+        <f>IF($A174="","",CHOOSE(WEEKDAY($A174),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C174" s="16" t="n"/>
@@ -4335,7 +4335,7 @@
     <row r="175">
       <c r="A175" s="14" t="n"/>
       <c r="B175" s="15">
-        <f>IF($A175="","",TEXT($A175,"aaa"))</f>
+        <f>IF($A175="","",CHOOSE(WEEKDAY($A175),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C175" s="16" t="n"/>
@@ -4355,7 +4355,7 @@
     <row r="176">
       <c r="A176" s="14" t="n"/>
       <c r="B176" s="15">
-        <f>IF($A176="","",TEXT($A176,"aaa"))</f>
+        <f>IF($A176="","",CHOOSE(WEEKDAY($A176),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C176" s="16" t="n"/>
@@ -4375,7 +4375,7 @@
     <row r="177">
       <c r="A177" s="14" t="n"/>
       <c r="B177" s="15">
-        <f>IF($A177="","",TEXT($A177,"aaa"))</f>
+        <f>IF($A177="","",CHOOSE(WEEKDAY($A177),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C177" s="16" t="n"/>
@@ -4395,7 +4395,7 @@
     <row r="178">
       <c r="A178" s="14" t="n"/>
       <c r="B178" s="15">
-        <f>IF($A178="","",TEXT($A178,"aaa"))</f>
+        <f>IF($A178="","",CHOOSE(WEEKDAY($A178),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C178" s="16" t="n"/>
@@ -4415,7 +4415,7 @@
     <row r="179">
       <c r="A179" s="14" t="n"/>
       <c r="B179" s="15">
-        <f>IF($A179="","",TEXT($A179,"aaa"))</f>
+        <f>IF($A179="","",CHOOSE(WEEKDAY($A179),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C179" s="16" t="n"/>
@@ -4435,7 +4435,7 @@
     <row r="180">
       <c r="A180" s="14" t="n"/>
       <c r="B180" s="15">
-        <f>IF($A180="","",TEXT($A180,"aaa"))</f>
+        <f>IF($A180="","",CHOOSE(WEEKDAY($A180),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C180" s="16" t="n"/>
@@ -4455,7 +4455,7 @@
     <row r="181">
       <c r="A181" s="14" t="n"/>
       <c r="B181" s="15">
-        <f>IF($A181="","",TEXT($A181,"aaa"))</f>
+        <f>IF($A181="","",CHOOSE(WEEKDAY($A181),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C181" s="16" t="n"/>
@@ -4475,7 +4475,7 @@
     <row r="182">
       <c r="A182" s="14" t="n"/>
       <c r="B182" s="15">
-        <f>IF($A182="","",TEXT($A182,"aaa"))</f>
+        <f>IF($A182="","",CHOOSE(WEEKDAY($A182),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C182" s="16" t="n"/>
@@ -4495,7 +4495,7 @@
     <row r="183">
       <c r="A183" s="14" t="n"/>
       <c r="B183" s="15">
-        <f>IF($A183="","",TEXT($A183,"aaa"))</f>
+        <f>IF($A183="","",CHOOSE(WEEKDAY($A183),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C183" s="16" t="n"/>
@@ -4515,7 +4515,7 @@
     <row r="184">
       <c r="A184" s="14" t="n"/>
       <c r="B184" s="15">
-        <f>IF($A184="","",TEXT($A184,"aaa"))</f>
+        <f>IF($A184="","",CHOOSE(WEEKDAY($A184),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C184" s="16" t="n"/>
@@ -4535,7 +4535,7 @@
     <row r="185">
       <c r="A185" s="14" t="n"/>
       <c r="B185" s="15">
-        <f>IF($A185="","",TEXT($A185,"aaa"))</f>
+        <f>IF($A185="","",CHOOSE(WEEKDAY($A185),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C185" s="16" t="n"/>
@@ -4555,7 +4555,7 @@
     <row r="186">
       <c r="A186" s="14" t="n"/>
       <c r="B186" s="15">
-        <f>IF($A186="","",TEXT($A186,"aaa"))</f>
+        <f>IF($A186="","",CHOOSE(WEEKDAY($A186),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C186" s="16" t="n"/>
@@ -4575,7 +4575,7 @@
     <row r="187">
       <c r="A187" s="14" t="n"/>
       <c r="B187" s="15">
-        <f>IF($A187="","",TEXT($A187,"aaa"))</f>
+        <f>IF($A187="","",CHOOSE(WEEKDAY($A187),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C187" s="16" t="n"/>
@@ -4595,7 +4595,7 @@
     <row r="188">
       <c r="A188" s="14" t="n"/>
       <c r="B188" s="15">
-        <f>IF($A188="","",TEXT($A188,"aaa"))</f>
+        <f>IF($A188="","",CHOOSE(WEEKDAY($A188),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C188" s="16" t="n"/>
@@ -4615,7 +4615,7 @@
     <row r="189">
       <c r="A189" s="14" t="n"/>
       <c r="B189" s="15">
-        <f>IF($A189="","",TEXT($A189,"aaa"))</f>
+        <f>IF($A189="","",CHOOSE(WEEKDAY($A189),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C189" s="16" t="n"/>
@@ -4635,7 +4635,7 @@
     <row r="190">
       <c r="A190" s="14" t="n"/>
       <c r="B190" s="15">
-        <f>IF($A190="","",TEXT($A190,"aaa"))</f>
+        <f>IF($A190="","",CHOOSE(WEEKDAY($A190),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C190" s="16" t="n"/>
@@ -4655,7 +4655,7 @@
     <row r="191">
       <c r="A191" s="14" t="n"/>
       <c r="B191" s="15">
-        <f>IF($A191="","",TEXT($A191,"aaa"))</f>
+        <f>IF($A191="","",CHOOSE(WEEKDAY($A191),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C191" s="16" t="n"/>
@@ -4675,7 +4675,7 @@
     <row r="192">
       <c r="A192" s="14" t="n"/>
       <c r="B192" s="15">
-        <f>IF($A192="","",TEXT($A192,"aaa"))</f>
+        <f>IF($A192="","",CHOOSE(WEEKDAY($A192),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C192" s="16" t="n"/>
@@ -4695,7 +4695,7 @@
     <row r="193">
       <c r="A193" s="14" t="n"/>
       <c r="B193" s="15">
-        <f>IF($A193="","",TEXT($A193,"aaa"))</f>
+        <f>IF($A193="","",CHOOSE(WEEKDAY($A193),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C193" s="16" t="n"/>
@@ -4715,7 +4715,7 @@
     <row r="194">
       <c r="A194" s="14" t="n"/>
       <c r="B194" s="15">
-        <f>IF($A194="","",TEXT($A194,"aaa"))</f>
+        <f>IF($A194="","",CHOOSE(WEEKDAY($A194),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C194" s="16" t="n"/>
@@ -4735,7 +4735,7 @@
     <row r="195">
       <c r="A195" s="14" t="n"/>
       <c r="B195" s="15">
-        <f>IF($A195="","",TEXT($A195,"aaa"))</f>
+        <f>IF($A195="","",CHOOSE(WEEKDAY($A195),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C195" s="16" t="n"/>
@@ -4755,7 +4755,7 @@
     <row r="196">
       <c r="A196" s="14" t="n"/>
       <c r="B196" s="15">
-        <f>IF($A196="","",TEXT($A196,"aaa"))</f>
+        <f>IF($A196="","",CHOOSE(WEEKDAY($A196),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C196" s="16" t="n"/>
@@ -4775,7 +4775,7 @@
     <row r="197">
       <c r="A197" s="14" t="n"/>
       <c r="B197" s="15">
-        <f>IF($A197="","",TEXT($A197,"aaa"))</f>
+        <f>IF($A197="","",CHOOSE(WEEKDAY($A197),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C197" s="16" t="n"/>
@@ -4795,7 +4795,7 @@
     <row r="198">
       <c r="A198" s="14" t="n"/>
       <c r="B198" s="15">
-        <f>IF($A198="","",TEXT($A198,"aaa"))</f>
+        <f>IF($A198="","",CHOOSE(WEEKDAY($A198),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C198" s="16" t="n"/>
@@ -4815,7 +4815,7 @@
     <row r="199">
       <c r="A199" s="14" t="n"/>
       <c r="B199" s="15">
-        <f>IF($A199="","",TEXT($A199,"aaa"))</f>
+        <f>IF($A199="","",CHOOSE(WEEKDAY($A199),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C199" s="16" t="n"/>
@@ -4835,7 +4835,7 @@
     <row r="200">
       <c r="A200" s="14" t="n"/>
       <c r="B200" s="15">
-        <f>IF($A200="","",TEXT($A200,"aaa"))</f>
+        <f>IF($A200="","",CHOOSE(WEEKDAY($A200),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C200" s="16" t="n"/>
@@ -4855,7 +4855,7 @@
     <row r="201">
       <c r="A201" s="14" t="n"/>
       <c r="B201" s="15">
-        <f>IF($A201="","",TEXT($A201,"aaa"))</f>
+        <f>IF($A201="","",CHOOSE(WEEKDAY($A201),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C201" s="16" t="n"/>
@@ -4875,7 +4875,7 @@
     <row r="202">
       <c r="A202" s="14" t="n"/>
       <c r="B202" s="15">
-        <f>IF($A202="","",TEXT($A202,"aaa"))</f>
+        <f>IF($A202="","",CHOOSE(WEEKDAY($A202),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C202" s="16" t="n"/>
@@ -4895,7 +4895,7 @@
     <row r="203">
       <c r="A203" s="14" t="n"/>
       <c r="B203" s="15">
-        <f>IF($A203="","",TEXT($A203,"aaa"))</f>
+        <f>IF($A203="","",CHOOSE(WEEKDAY($A203),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C203" s="16" t="n"/>
@@ -4915,7 +4915,7 @@
     <row r="204">
       <c r="A204" s="14" t="n"/>
       <c r="B204" s="15">
-        <f>IF($A204="","",TEXT($A204,"aaa"))</f>
+        <f>IF($A204="","",CHOOSE(WEEKDAY($A204),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C204" s="16" t="n"/>
@@ -4935,7 +4935,7 @@
     <row r="205">
       <c r="A205" s="14" t="n"/>
       <c r="B205" s="15">
-        <f>IF($A205="","",TEXT($A205,"aaa"))</f>
+        <f>IF($A205="","",CHOOSE(WEEKDAY($A205),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C205" s="16" t="n"/>
@@ -4955,7 +4955,7 @@
     <row r="206">
       <c r="A206" s="14" t="n"/>
       <c r="B206" s="15">
-        <f>IF($A206="","",TEXT($A206,"aaa"))</f>
+        <f>IF($A206="","",CHOOSE(WEEKDAY($A206),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C206" s="16" t="n"/>
@@ -4975,7 +4975,7 @@
     <row r="207">
       <c r="A207" s="14" t="n"/>
       <c r="B207" s="15">
-        <f>IF($A207="","",TEXT($A207,"aaa"))</f>
+        <f>IF($A207="","",CHOOSE(WEEKDAY($A207),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C207" s="16" t="n"/>
@@ -4995,7 +4995,7 @@
     <row r="208">
       <c r="A208" s="14" t="n"/>
       <c r="B208" s="15">
-        <f>IF($A208="","",TEXT($A208,"aaa"))</f>
+        <f>IF($A208="","",CHOOSE(WEEKDAY($A208),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C208" s="16" t="n"/>
@@ -5015,7 +5015,7 @@
     <row r="209">
       <c r="A209" s="14" t="n"/>
       <c r="B209" s="15">
-        <f>IF($A209="","",TEXT($A209,"aaa"))</f>
+        <f>IF($A209="","",CHOOSE(WEEKDAY($A209),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C209" s="16" t="n"/>
@@ -5035,7 +5035,7 @@
     <row r="210">
       <c r="A210" s="14" t="n"/>
       <c r="B210" s="15">
-        <f>IF($A210="","",TEXT($A210,"aaa"))</f>
+        <f>IF($A210="","",CHOOSE(WEEKDAY($A210),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C210" s="16" t="n"/>
@@ -5055,7 +5055,7 @@
     <row r="211">
       <c r="A211" s="14" t="n"/>
       <c r="B211" s="15">
-        <f>IF($A211="","",TEXT($A211,"aaa"))</f>
+        <f>IF($A211="","",CHOOSE(WEEKDAY($A211),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C211" s="16" t="n"/>
@@ -5075,7 +5075,7 @@
     <row r="212">
       <c r="A212" s="14" t="n"/>
       <c r="B212" s="15">
-        <f>IF($A212="","",TEXT($A212,"aaa"))</f>
+        <f>IF($A212="","",CHOOSE(WEEKDAY($A212),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C212" s="16" t="n"/>
@@ -5095,7 +5095,7 @@
     <row r="213">
       <c r="A213" s="14" t="n"/>
       <c r="B213" s="15">
-        <f>IF($A213="","",TEXT($A213,"aaa"))</f>
+        <f>IF($A213="","",CHOOSE(WEEKDAY($A213),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C213" s="16" t="n"/>
@@ -5115,7 +5115,7 @@
     <row r="214">
       <c r="A214" s="14" t="n"/>
       <c r="B214" s="15">
-        <f>IF($A214="","",TEXT($A214,"aaa"))</f>
+        <f>IF($A214="","",CHOOSE(WEEKDAY($A214),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C214" s="16" t="n"/>
@@ -5135,7 +5135,7 @@
     <row r="215">
       <c r="A215" s="14" t="n"/>
       <c r="B215" s="15">
-        <f>IF($A215="","",TEXT($A215,"aaa"))</f>
+        <f>IF($A215="","",CHOOSE(WEEKDAY($A215),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C215" s="16" t="n"/>
@@ -5155,7 +5155,7 @@
     <row r="216">
       <c r="A216" s="14" t="n"/>
       <c r="B216" s="15">
-        <f>IF($A216="","",TEXT($A216,"aaa"))</f>
+        <f>IF($A216="","",CHOOSE(WEEKDAY($A216),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C216" s="16" t="n"/>
@@ -5175,7 +5175,7 @@
     <row r="217">
       <c r="A217" s="14" t="n"/>
       <c r="B217" s="15">
-        <f>IF($A217="","",TEXT($A217,"aaa"))</f>
+        <f>IF($A217="","",CHOOSE(WEEKDAY($A217),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C217" s="16" t="n"/>
@@ -5195,7 +5195,7 @@
     <row r="218">
       <c r="A218" s="14" t="n"/>
       <c r="B218" s="15">
-        <f>IF($A218="","",TEXT($A218,"aaa"))</f>
+        <f>IF($A218="","",CHOOSE(WEEKDAY($A218),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C218" s="16" t="n"/>
@@ -5215,7 +5215,7 @@
     <row r="219">
       <c r="A219" s="14" t="n"/>
       <c r="B219" s="15">
-        <f>IF($A219="","",TEXT($A219,"aaa"))</f>
+        <f>IF($A219="","",CHOOSE(WEEKDAY($A219),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C219" s="16" t="n"/>
@@ -5235,7 +5235,7 @@
     <row r="220">
       <c r="A220" s="14" t="n"/>
       <c r="B220" s="15">
-        <f>IF($A220="","",TEXT($A220,"aaa"))</f>
+        <f>IF($A220="","",CHOOSE(WEEKDAY($A220),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C220" s="16" t="n"/>
@@ -5255,7 +5255,7 @@
     <row r="221">
       <c r="A221" s="14" t="n"/>
       <c r="B221" s="15">
-        <f>IF($A221="","",TEXT($A221,"aaa"))</f>
+        <f>IF($A221="","",CHOOSE(WEEKDAY($A221),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C221" s="16" t="n"/>
@@ -5275,7 +5275,7 @@
     <row r="222">
       <c r="A222" s="14" t="n"/>
       <c r="B222" s="15">
-        <f>IF($A222="","",TEXT($A222,"aaa"))</f>
+        <f>IF($A222="","",CHOOSE(WEEKDAY($A222),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C222" s="16" t="n"/>
@@ -5295,7 +5295,7 @@
     <row r="223">
       <c r="A223" s="14" t="n"/>
       <c r="B223" s="15">
-        <f>IF($A223="","",TEXT($A223,"aaa"))</f>
+        <f>IF($A223="","",CHOOSE(WEEKDAY($A223),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C223" s="16" t="n"/>
@@ -5315,7 +5315,7 @@
     <row r="224">
       <c r="A224" s="14" t="n"/>
       <c r="B224" s="15">
-        <f>IF($A224="","",TEXT($A224,"aaa"))</f>
+        <f>IF($A224="","",CHOOSE(WEEKDAY($A224),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C224" s="16" t="n"/>
@@ -5335,7 +5335,7 @@
     <row r="225">
       <c r="A225" s="14" t="n"/>
       <c r="B225" s="15">
-        <f>IF($A225="","",TEXT($A225,"aaa"))</f>
+        <f>IF($A225="","",CHOOSE(WEEKDAY($A225),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C225" s="16" t="n"/>
@@ -5355,7 +5355,7 @@
     <row r="226">
       <c r="A226" s="14" t="n"/>
       <c r="B226" s="15">
-        <f>IF($A226="","",TEXT($A226,"aaa"))</f>
+        <f>IF($A226="","",CHOOSE(WEEKDAY($A226),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C226" s="16" t="n"/>
@@ -5375,7 +5375,7 @@
     <row r="227">
       <c r="A227" s="14" t="n"/>
       <c r="B227" s="15">
-        <f>IF($A227="","",TEXT($A227,"aaa"))</f>
+        <f>IF($A227="","",CHOOSE(WEEKDAY($A227),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C227" s="16" t="n"/>
@@ -5395,7 +5395,7 @@
     <row r="228">
       <c r="A228" s="14" t="n"/>
       <c r="B228" s="15">
-        <f>IF($A228="","",TEXT($A228,"aaa"))</f>
+        <f>IF($A228="","",CHOOSE(WEEKDAY($A228),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C228" s="16" t="n"/>
@@ -5415,7 +5415,7 @@
     <row r="229">
       <c r="A229" s="14" t="n"/>
       <c r="B229" s="15">
-        <f>IF($A229="","",TEXT($A229,"aaa"))</f>
+        <f>IF($A229="","",CHOOSE(WEEKDAY($A229),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C229" s="16" t="n"/>
@@ -5435,7 +5435,7 @@
     <row r="230">
       <c r="A230" s="14" t="n"/>
       <c r="B230" s="15">
-        <f>IF($A230="","",TEXT($A230,"aaa"))</f>
+        <f>IF($A230="","",CHOOSE(WEEKDAY($A230),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C230" s="16" t="n"/>
@@ -5455,7 +5455,7 @@
     <row r="231">
       <c r="A231" s="14" t="n"/>
       <c r="B231" s="15">
-        <f>IF($A231="","",TEXT($A231,"aaa"))</f>
+        <f>IF($A231="","",CHOOSE(WEEKDAY($A231),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C231" s="16" t="n"/>
@@ -5475,7 +5475,7 @@
     <row r="232">
       <c r="A232" s="14" t="n"/>
       <c r="B232" s="15">
-        <f>IF($A232="","",TEXT($A232,"aaa"))</f>
+        <f>IF($A232="","",CHOOSE(WEEKDAY($A232),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C232" s="16" t="n"/>
@@ -5495,7 +5495,7 @@
     <row r="233">
       <c r="A233" s="14" t="n"/>
       <c r="B233" s="15">
-        <f>IF($A233="","",TEXT($A233,"aaa"))</f>
+        <f>IF($A233="","",CHOOSE(WEEKDAY($A233),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C233" s="16" t="n"/>
@@ -5515,7 +5515,7 @@
     <row r="234">
       <c r="A234" s="14" t="n"/>
       <c r="B234" s="15">
-        <f>IF($A234="","",TEXT($A234,"aaa"))</f>
+        <f>IF($A234="","",CHOOSE(WEEKDAY($A234),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C234" s="16" t="n"/>
@@ -5535,7 +5535,7 @@
     <row r="235">
       <c r="A235" s="14" t="n"/>
       <c r="B235" s="15">
-        <f>IF($A235="","",TEXT($A235,"aaa"))</f>
+        <f>IF($A235="","",CHOOSE(WEEKDAY($A235),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C235" s="16" t="n"/>
@@ -5555,7 +5555,7 @@
     <row r="236">
       <c r="A236" s="14" t="n"/>
       <c r="B236" s="15">
-        <f>IF($A236="","",TEXT($A236,"aaa"))</f>
+        <f>IF($A236="","",CHOOSE(WEEKDAY($A236),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C236" s="16" t="n"/>
@@ -5575,7 +5575,7 @@
     <row r="237">
       <c r="A237" s="14" t="n"/>
       <c r="B237" s="15">
-        <f>IF($A237="","",TEXT($A237,"aaa"))</f>
+        <f>IF($A237="","",CHOOSE(WEEKDAY($A237),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C237" s="16" t="n"/>
@@ -5595,7 +5595,7 @@
     <row r="238">
       <c r="A238" s="14" t="n"/>
       <c r="B238" s="15">
-        <f>IF($A238="","",TEXT($A238,"aaa"))</f>
+        <f>IF($A238="","",CHOOSE(WEEKDAY($A238),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C238" s="16" t="n"/>
@@ -5615,7 +5615,7 @@
     <row r="239">
       <c r="A239" s="14" t="n"/>
       <c r="B239" s="15">
-        <f>IF($A239="","",TEXT($A239,"aaa"))</f>
+        <f>IF($A239="","",CHOOSE(WEEKDAY($A239),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C239" s="16" t="n"/>
@@ -5635,7 +5635,7 @@
     <row r="240">
       <c r="A240" s="14" t="n"/>
       <c r="B240" s="15">
-        <f>IF($A240="","",TEXT($A240,"aaa"))</f>
+        <f>IF($A240="","",CHOOSE(WEEKDAY($A240),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C240" s="16" t="n"/>
@@ -5655,7 +5655,7 @@
     <row r="241">
       <c r="A241" s="14" t="n"/>
       <c r="B241" s="15">
-        <f>IF($A241="","",TEXT($A241,"aaa"))</f>
+        <f>IF($A241="","",CHOOSE(WEEKDAY($A241),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C241" s="16" t="n"/>
@@ -5675,7 +5675,7 @@
     <row r="242">
       <c r="A242" s="14" t="n"/>
       <c r="B242" s="15">
-        <f>IF($A242="","",TEXT($A242,"aaa"))</f>
+        <f>IF($A242="","",CHOOSE(WEEKDAY($A242),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C242" s="16" t="n"/>
@@ -5695,7 +5695,7 @@
     <row r="243">
       <c r="A243" s="14" t="n"/>
       <c r="B243" s="15">
-        <f>IF($A243="","",TEXT($A243,"aaa"))</f>
+        <f>IF($A243="","",CHOOSE(WEEKDAY($A243),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C243" s="16" t="n"/>
@@ -5715,7 +5715,7 @@
     <row r="244">
       <c r="A244" s="14" t="n"/>
       <c r="B244" s="15">
-        <f>IF($A244="","",TEXT($A244,"aaa"))</f>
+        <f>IF($A244="","",CHOOSE(WEEKDAY($A244),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C244" s="16" t="n"/>
@@ -5735,7 +5735,7 @@
     <row r="245">
       <c r="A245" s="14" t="n"/>
       <c r="B245" s="15">
-        <f>IF($A245="","",TEXT($A245,"aaa"))</f>
+        <f>IF($A245="","",CHOOSE(WEEKDAY($A245),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C245" s="16" t="n"/>
@@ -5755,7 +5755,7 @@
     <row r="246">
       <c r="A246" s="14" t="n"/>
       <c r="B246" s="15">
-        <f>IF($A246="","",TEXT($A246,"aaa"))</f>
+        <f>IF($A246="","",CHOOSE(WEEKDAY($A246),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C246" s="16" t="n"/>
@@ -5775,7 +5775,7 @@
     <row r="247">
       <c r="A247" s="14" t="n"/>
       <c r="B247" s="15">
-        <f>IF($A247="","",TEXT($A247,"aaa"))</f>
+        <f>IF($A247="","",CHOOSE(WEEKDAY($A247),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C247" s="16" t="n"/>
@@ -5795,7 +5795,7 @@
     <row r="248">
       <c r="A248" s="14" t="n"/>
       <c r="B248" s="15">
-        <f>IF($A248="","",TEXT($A248,"aaa"))</f>
+        <f>IF($A248="","",CHOOSE(WEEKDAY($A248),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C248" s="16" t="n"/>
@@ -5815,7 +5815,7 @@
     <row r="249">
       <c r="A249" s="14" t="n"/>
       <c r="B249" s="15">
-        <f>IF($A249="","",TEXT($A249,"aaa"))</f>
+        <f>IF($A249="","",CHOOSE(WEEKDAY($A249),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C249" s="16" t="n"/>
@@ -5835,7 +5835,7 @@
     <row r="250">
       <c r="A250" s="14" t="n"/>
       <c r="B250" s="15">
-        <f>IF($A250="","",TEXT($A250,"aaa"))</f>
+        <f>IF($A250="","",CHOOSE(WEEKDAY($A250),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C250" s="16" t="n"/>
@@ -5855,7 +5855,7 @@
     <row r="251">
       <c r="A251" s="14" t="n"/>
       <c r="B251" s="15">
-        <f>IF($A251="","",TEXT($A251,"aaa"))</f>
+        <f>IF($A251="","",CHOOSE(WEEKDAY($A251),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C251" s="16" t="n"/>
@@ -5875,7 +5875,7 @@
     <row r="252">
       <c r="A252" s="14" t="n"/>
       <c r="B252" s="15">
-        <f>IF($A252="","",TEXT($A252,"aaa"))</f>
+        <f>IF($A252="","",CHOOSE(WEEKDAY($A252),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C252" s="16" t="n"/>
@@ -5895,7 +5895,7 @@
     <row r="253">
       <c r="A253" s="14" t="n"/>
       <c r="B253" s="15">
-        <f>IF($A253="","",TEXT($A253,"aaa"))</f>
+        <f>IF($A253="","",CHOOSE(WEEKDAY($A253),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C253" s="16" t="n"/>
@@ -5915,7 +5915,7 @@
     <row r="254">
       <c r="A254" s="14" t="n"/>
       <c r="B254" s="15">
-        <f>IF($A254="","",TEXT($A254,"aaa"))</f>
+        <f>IF($A254="","",CHOOSE(WEEKDAY($A254),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C254" s="16" t="n"/>
@@ -5935,7 +5935,7 @@
     <row r="255">
       <c r="A255" s="14" t="n"/>
       <c r="B255" s="15">
-        <f>IF($A255="","",TEXT($A255,"aaa"))</f>
+        <f>IF($A255="","",CHOOSE(WEEKDAY($A255),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C255" s="16" t="n"/>
@@ -5955,7 +5955,7 @@
     <row r="256">
       <c r="A256" s="14" t="n"/>
       <c r="B256" s="15">
-        <f>IF($A256="","",TEXT($A256,"aaa"))</f>
+        <f>IF($A256="","",CHOOSE(WEEKDAY($A256),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C256" s="16" t="n"/>
@@ -5975,7 +5975,7 @@
     <row r="257">
       <c r="A257" s="14" t="n"/>
       <c r="B257" s="15">
-        <f>IF($A257="","",TEXT($A257,"aaa"))</f>
+        <f>IF($A257="","",CHOOSE(WEEKDAY($A257),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C257" s="16" t="n"/>
@@ -5995,7 +5995,7 @@
     <row r="258">
       <c r="A258" s="14" t="n"/>
       <c r="B258" s="15">
-        <f>IF($A258="","",TEXT($A258,"aaa"))</f>
+        <f>IF($A258="","",CHOOSE(WEEKDAY($A258),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C258" s="16" t="n"/>
@@ -6015,7 +6015,7 @@
     <row r="259">
       <c r="A259" s="14" t="n"/>
       <c r="B259" s="15">
-        <f>IF($A259="","",TEXT($A259,"aaa"))</f>
+        <f>IF($A259="","",CHOOSE(WEEKDAY($A259),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C259" s="16" t="n"/>
@@ -6035,7 +6035,7 @@
     <row r="260">
       <c r="A260" s="14" t="n"/>
       <c r="B260" s="15">
-        <f>IF($A260="","",TEXT($A260,"aaa"))</f>
+        <f>IF($A260="","",CHOOSE(WEEKDAY($A260),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C260" s="16" t="n"/>
@@ -6055,7 +6055,7 @@
     <row r="261">
       <c r="A261" s="14" t="n"/>
       <c r="B261" s="15">
-        <f>IF($A261="","",TEXT($A261,"aaa"))</f>
+        <f>IF($A261="","",CHOOSE(WEEKDAY($A261),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C261" s="16" t="n"/>
@@ -6075,7 +6075,7 @@
     <row r="262">
       <c r="A262" s="14" t="n"/>
       <c r="B262" s="15">
-        <f>IF($A262="","",TEXT($A262,"aaa"))</f>
+        <f>IF($A262="","",CHOOSE(WEEKDAY($A262),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C262" s="16" t="n"/>
@@ -6095,7 +6095,7 @@
     <row r="263">
       <c r="A263" s="14" t="n"/>
       <c r="B263" s="15">
-        <f>IF($A263="","",TEXT($A263,"aaa"))</f>
+        <f>IF($A263="","",CHOOSE(WEEKDAY($A263),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C263" s="16" t="n"/>
@@ -6115,7 +6115,7 @@
     <row r="264">
       <c r="A264" s="14" t="n"/>
       <c r="B264" s="15">
-        <f>IF($A264="","",TEXT($A264,"aaa"))</f>
+        <f>IF($A264="","",CHOOSE(WEEKDAY($A264),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C264" s="16" t="n"/>
@@ -6135,7 +6135,7 @@
     <row r="265">
       <c r="A265" s="14" t="n"/>
       <c r="B265" s="15">
-        <f>IF($A265="","",TEXT($A265,"aaa"))</f>
+        <f>IF($A265="","",CHOOSE(WEEKDAY($A265),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C265" s="16" t="n"/>
@@ -6155,7 +6155,7 @@
     <row r="266">
       <c r="A266" s="14" t="n"/>
       <c r="B266" s="15">
-        <f>IF($A266="","",TEXT($A266,"aaa"))</f>
+        <f>IF($A266="","",CHOOSE(WEEKDAY($A266),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C266" s="16" t="n"/>
@@ -6175,7 +6175,7 @@
     <row r="267">
       <c r="A267" s="14" t="n"/>
       <c r="B267" s="15">
-        <f>IF($A267="","",TEXT($A267,"aaa"))</f>
+        <f>IF($A267="","",CHOOSE(WEEKDAY($A267),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C267" s="16" t="n"/>
@@ -6195,7 +6195,7 @@
     <row r="268">
       <c r="A268" s="14" t="n"/>
       <c r="B268" s="15">
-        <f>IF($A268="","",TEXT($A268,"aaa"))</f>
+        <f>IF($A268="","",CHOOSE(WEEKDAY($A268),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C268" s="16" t="n"/>
@@ -6215,7 +6215,7 @@
     <row r="269">
       <c r="A269" s="14" t="n"/>
       <c r="B269" s="15">
-        <f>IF($A269="","",TEXT($A269,"aaa"))</f>
+        <f>IF($A269="","",CHOOSE(WEEKDAY($A269),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C269" s="16" t="n"/>
@@ -6235,7 +6235,7 @@
     <row r="270">
       <c r="A270" s="14" t="n"/>
       <c r="B270" s="15">
-        <f>IF($A270="","",TEXT($A270,"aaa"))</f>
+        <f>IF($A270="","",CHOOSE(WEEKDAY($A270),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C270" s="16" t="n"/>
@@ -6255,7 +6255,7 @@
     <row r="271">
       <c r="A271" s="14" t="n"/>
       <c r="B271" s="15">
-        <f>IF($A271="","",TEXT($A271,"aaa"))</f>
+        <f>IF($A271="","",CHOOSE(WEEKDAY($A271),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C271" s="16" t="n"/>
@@ -6275,7 +6275,7 @@
     <row r="272">
       <c r="A272" s="14" t="n"/>
       <c r="B272" s="15">
-        <f>IF($A272="","",TEXT($A272,"aaa"))</f>
+        <f>IF($A272="","",CHOOSE(WEEKDAY($A272),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C272" s="16" t="n"/>
@@ -6295,7 +6295,7 @@
     <row r="273">
       <c r="A273" s="14" t="n"/>
       <c r="B273" s="15">
-        <f>IF($A273="","",TEXT($A273,"aaa"))</f>
+        <f>IF($A273="","",CHOOSE(WEEKDAY($A273),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C273" s="16" t="n"/>
@@ -6315,7 +6315,7 @@
     <row r="274">
       <c r="A274" s="14" t="n"/>
       <c r="B274" s="15">
-        <f>IF($A274="","",TEXT($A274,"aaa"))</f>
+        <f>IF($A274="","",CHOOSE(WEEKDAY($A274),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C274" s="16" t="n"/>
@@ -6335,7 +6335,7 @@
     <row r="275">
       <c r="A275" s="14" t="n"/>
       <c r="B275" s="15">
-        <f>IF($A275="","",TEXT($A275,"aaa"))</f>
+        <f>IF($A275="","",CHOOSE(WEEKDAY($A275),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C275" s="16" t="n"/>
@@ -6355,7 +6355,7 @@
     <row r="276">
       <c r="A276" s="14" t="n"/>
       <c r="B276" s="15">
-        <f>IF($A276="","",TEXT($A276,"aaa"))</f>
+        <f>IF($A276="","",CHOOSE(WEEKDAY($A276),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C276" s="16" t="n"/>
@@ -6375,7 +6375,7 @@
     <row r="277">
       <c r="A277" s="14" t="n"/>
       <c r="B277" s="15">
-        <f>IF($A277="","",TEXT($A277,"aaa"))</f>
+        <f>IF($A277="","",CHOOSE(WEEKDAY($A277),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C277" s="16" t="n"/>
@@ -6395,7 +6395,7 @@
     <row r="278">
       <c r="A278" s="14" t="n"/>
       <c r="B278" s="15">
-        <f>IF($A278="","",TEXT($A278,"aaa"))</f>
+        <f>IF($A278="","",CHOOSE(WEEKDAY($A278),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C278" s="16" t="n"/>
@@ -6415,7 +6415,7 @@
     <row r="279">
       <c r="A279" s="14" t="n"/>
       <c r="B279" s="15">
-        <f>IF($A279="","",TEXT($A279,"aaa"))</f>
+        <f>IF($A279="","",CHOOSE(WEEKDAY($A279),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C279" s="16" t="n"/>
@@ -6435,7 +6435,7 @@
     <row r="280">
       <c r="A280" s="14" t="n"/>
       <c r="B280" s="15">
-        <f>IF($A280="","",TEXT($A280,"aaa"))</f>
+        <f>IF($A280="","",CHOOSE(WEEKDAY($A280),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C280" s="16" t="n"/>
@@ -6455,7 +6455,7 @@
     <row r="281">
       <c r="A281" s="14" t="n"/>
       <c r="B281" s="15">
-        <f>IF($A281="","",TEXT($A281,"aaa"))</f>
+        <f>IF($A281="","",CHOOSE(WEEKDAY($A281),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C281" s="16" t="n"/>
@@ -6475,7 +6475,7 @@
     <row r="282">
       <c r="A282" s="14" t="n"/>
       <c r="B282" s="15">
-        <f>IF($A282="","",TEXT($A282,"aaa"))</f>
+        <f>IF($A282="","",CHOOSE(WEEKDAY($A282),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C282" s="16" t="n"/>
@@ -6495,7 +6495,7 @@
     <row r="283">
       <c r="A283" s="14" t="n"/>
       <c r="B283" s="15">
-        <f>IF($A283="","",TEXT($A283,"aaa"))</f>
+        <f>IF($A283="","",CHOOSE(WEEKDAY($A283),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C283" s="16" t="n"/>
@@ -6515,7 +6515,7 @@
     <row r="284">
       <c r="A284" s="14" t="n"/>
       <c r="B284" s="15">
-        <f>IF($A284="","",TEXT($A284,"aaa"))</f>
+        <f>IF($A284="","",CHOOSE(WEEKDAY($A284),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C284" s="16" t="n"/>
@@ -6535,7 +6535,7 @@
     <row r="285">
       <c r="A285" s="14" t="n"/>
       <c r="B285" s="15">
-        <f>IF($A285="","",TEXT($A285,"aaa"))</f>
+        <f>IF($A285="","",CHOOSE(WEEKDAY($A285),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C285" s="16" t="n"/>
@@ -6555,7 +6555,7 @@
     <row r="286">
       <c r="A286" s="14" t="n"/>
       <c r="B286" s="15">
-        <f>IF($A286="","",TEXT($A286,"aaa"))</f>
+        <f>IF($A286="","",CHOOSE(WEEKDAY($A286),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C286" s="16" t="n"/>
@@ -6575,7 +6575,7 @@
     <row r="287">
       <c r="A287" s="14" t="n"/>
       <c r="B287" s="15">
-        <f>IF($A287="","",TEXT($A287,"aaa"))</f>
+        <f>IF($A287="","",CHOOSE(WEEKDAY($A287),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C287" s="16" t="n"/>
@@ -6595,7 +6595,7 @@
     <row r="288">
       <c r="A288" s="14" t="n"/>
       <c r="B288" s="15">
-        <f>IF($A288="","",TEXT($A288,"aaa"))</f>
+        <f>IF($A288="","",CHOOSE(WEEKDAY($A288),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C288" s="16" t="n"/>
@@ -6615,7 +6615,7 @@
     <row r="289">
       <c r="A289" s="14" t="n"/>
       <c r="B289" s="15">
-        <f>IF($A289="","",TEXT($A289,"aaa"))</f>
+        <f>IF($A289="","",CHOOSE(WEEKDAY($A289),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C289" s="16" t="n"/>
@@ -6635,7 +6635,7 @@
     <row r="290">
       <c r="A290" s="14" t="n"/>
       <c r="B290" s="15">
-        <f>IF($A290="","",TEXT($A290,"aaa"))</f>
+        <f>IF($A290="","",CHOOSE(WEEKDAY($A290),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C290" s="16" t="n"/>
@@ -6655,7 +6655,7 @@
     <row r="291">
       <c r="A291" s="14" t="n"/>
       <c r="B291" s="15">
-        <f>IF($A291="","",TEXT($A291,"aaa"))</f>
+        <f>IF($A291="","",CHOOSE(WEEKDAY($A291),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C291" s="16" t="n"/>
@@ -6675,7 +6675,7 @@
     <row r="292">
       <c r="A292" s="14" t="n"/>
       <c r="B292" s="15">
-        <f>IF($A292="","",TEXT($A292,"aaa"))</f>
+        <f>IF($A292="","",CHOOSE(WEEKDAY($A292),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C292" s="16" t="n"/>
@@ -6695,7 +6695,7 @@
     <row r="293">
       <c r="A293" s="14" t="n"/>
       <c r="B293" s="15">
-        <f>IF($A293="","",TEXT($A293,"aaa"))</f>
+        <f>IF($A293="","",CHOOSE(WEEKDAY($A293),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C293" s="16" t="n"/>
@@ -6715,7 +6715,7 @@
     <row r="294">
       <c r="A294" s="14" t="n"/>
       <c r="B294" s="15">
-        <f>IF($A294="","",TEXT($A294,"aaa"))</f>
+        <f>IF($A294="","",CHOOSE(WEEKDAY($A294),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C294" s="16" t="n"/>
@@ -6735,7 +6735,7 @@
     <row r="295">
       <c r="A295" s="14" t="n"/>
       <c r="B295" s="15">
-        <f>IF($A295="","",TEXT($A295,"aaa"))</f>
+        <f>IF($A295="","",CHOOSE(WEEKDAY($A295),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C295" s="16" t="n"/>
@@ -6755,7 +6755,7 @@
     <row r="296">
       <c r="A296" s="14" t="n"/>
       <c r="B296" s="15">
-        <f>IF($A296="","",TEXT($A296,"aaa"))</f>
+        <f>IF($A296="","",CHOOSE(WEEKDAY($A296),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C296" s="16" t="n"/>
@@ -6775,7 +6775,7 @@
     <row r="297">
       <c r="A297" s="14" t="n"/>
       <c r="B297" s="15">
-        <f>IF($A297="","",TEXT($A297,"aaa"))</f>
+        <f>IF($A297="","",CHOOSE(WEEKDAY($A297),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C297" s="16" t="n"/>
@@ -6795,7 +6795,7 @@
     <row r="298">
       <c r="A298" s="14" t="n"/>
       <c r="B298" s="15">
-        <f>IF($A298="","",TEXT($A298,"aaa"))</f>
+        <f>IF($A298="","",CHOOSE(WEEKDAY($A298),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C298" s="16" t="n"/>
@@ -6815,7 +6815,7 @@
     <row r="299">
       <c r="A299" s="14" t="n"/>
       <c r="B299" s="15">
-        <f>IF($A299="","",TEXT($A299,"aaa"))</f>
+        <f>IF($A299="","",CHOOSE(WEEKDAY($A299),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C299" s="16" t="n"/>
@@ -6835,7 +6835,7 @@
     <row r="300">
       <c r="A300" s="14" t="n"/>
       <c r="B300" s="15">
-        <f>IF($A300="","",TEXT($A300,"aaa"))</f>
+        <f>IF($A300="","",CHOOSE(WEEKDAY($A300),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C300" s="16" t="n"/>
@@ -6855,7 +6855,7 @@
     <row r="301">
       <c r="A301" s="14" t="n"/>
       <c r="B301" s="15">
-        <f>IF($A301="","",TEXT($A301,"aaa"))</f>
+        <f>IF($A301="","",CHOOSE(WEEKDAY($A301),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C301" s="16" t="n"/>
@@ -6875,7 +6875,7 @@
     <row r="302">
       <c r="A302" s="14" t="n"/>
       <c r="B302" s="15">
-        <f>IF($A302="","",TEXT($A302,"aaa"))</f>
+        <f>IF($A302="","",CHOOSE(WEEKDAY($A302),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C302" s="16" t="n"/>
@@ -6895,7 +6895,7 @@
     <row r="303">
       <c r="A303" s="14" t="n"/>
       <c r="B303" s="15">
-        <f>IF($A303="","",TEXT($A303,"aaa"))</f>
+        <f>IF($A303="","",CHOOSE(WEEKDAY($A303),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C303" s="16" t="n"/>
@@ -6915,7 +6915,7 @@
     <row r="304">
       <c r="A304" s="14" t="n"/>
       <c r="B304" s="15">
-        <f>IF($A304="","",TEXT($A304,"aaa"))</f>
+        <f>IF($A304="","",CHOOSE(WEEKDAY($A304),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C304" s="16" t="n"/>
@@ -6935,7 +6935,7 @@
     <row r="305">
       <c r="A305" s="14" t="n"/>
       <c r="B305" s="15">
-        <f>IF($A305="","",TEXT($A305,"aaa"))</f>
+        <f>IF($A305="","",CHOOSE(WEEKDAY($A305),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C305" s="16" t="n"/>
@@ -6955,7 +6955,7 @@
     <row r="306">
       <c r="A306" s="14" t="n"/>
       <c r="B306" s="15">
-        <f>IF($A306="","",TEXT($A306,"aaa"))</f>
+        <f>IF($A306="","",CHOOSE(WEEKDAY($A306),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C306" s="16" t="n"/>
@@ -6975,7 +6975,7 @@
     <row r="307">
       <c r="A307" s="14" t="n"/>
       <c r="B307" s="15">
-        <f>IF($A307="","",TEXT($A307,"aaa"))</f>
+        <f>IF($A307="","",CHOOSE(WEEKDAY($A307),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C307" s="16" t="n"/>
@@ -6995,7 +6995,7 @@
     <row r="308">
       <c r="A308" s="14" t="n"/>
       <c r="B308" s="15">
-        <f>IF($A308="","",TEXT($A308,"aaa"))</f>
+        <f>IF($A308="","",CHOOSE(WEEKDAY($A308),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C308" s="16" t="n"/>
@@ -7015,7 +7015,7 @@
     <row r="309">
       <c r="A309" s="14" t="n"/>
       <c r="B309" s="15">
-        <f>IF($A309="","",TEXT($A309,"aaa"))</f>
+        <f>IF($A309="","",CHOOSE(WEEKDAY($A309),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C309" s="16" t="n"/>
@@ -7035,7 +7035,7 @@
     <row r="310">
       <c r="A310" s="14" t="n"/>
       <c r="B310" s="15">
-        <f>IF($A310="","",TEXT($A310,"aaa"))</f>
+        <f>IF($A310="","",CHOOSE(WEEKDAY($A310),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C310" s="16" t="n"/>
@@ -7055,7 +7055,7 @@
     <row r="311">
       <c r="A311" s="14" t="n"/>
       <c r="B311" s="15">
-        <f>IF($A311="","",TEXT($A311,"aaa"))</f>
+        <f>IF($A311="","",CHOOSE(WEEKDAY($A311),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C311" s="16" t="n"/>
@@ -7075,7 +7075,7 @@
     <row r="312">
       <c r="A312" s="14" t="n"/>
       <c r="B312" s="15">
-        <f>IF($A312="","",TEXT($A312,"aaa"))</f>
+        <f>IF($A312="","",CHOOSE(WEEKDAY($A312),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C312" s="16" t="n"/>
@@ -7095,7 +7095,7 @@
     <row r="313">
       <c r="A313" s="14" t="n"/>
       <c r="B313" s="15">
-        <f>IF($A313="","",TEXT($A313,"aaa"))</f>
+        <f>IF($A313="","",CHOOSE(WEEKDAY($A313),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C313" s="16" t="n"/>
@@ -7115,7 +7115,7 @@
     <row r="314">
       <c r="A314" s="14" t="n"/>
       <c r="B314" s="15">
-        <f>IF($A314="","",TEXT($A314,"aaa"))</f>
+        <f>IF($A314="","",CHOOSE(WEEKDAY($A314),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C314" s="16" t="n"/>
@@ -7135,7 +7135,7 @@
     <row r="315">
       <c r="A315" s="14" t="n"/>
       <c r="B315" s="15">
-        <f>IF($A315="","",TEXT($A315,"aaa"))</f>
+        <f>IF($A315="","",CHOOSE(WEEKDAY($A315),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C315" s="16" t="n"/>
@@ -7155,7 +7155,7 @@
     <row r="316">
       <c r="A316" s="14" t="n"/>
       <c r="B316" s="15">
-        <f>IF($A316="","",TEXT($A316,"aaa"))</f>
+        <f>IF($A316="","",CHOOSE(WEEKDAY($A316),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C316" s="16" t="n"/>
@@ -7175,7 +7175,7 @@
     <row r="317">
       <c r="A317" s="14" t="n"/>
       <c r="B317" s="15">
-        <f>IF($A317="","",TEXT($A317,"aaa"))</f>
+        <f>IF($A317="","",CHOOSE(WEEKDAY($A317),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C317" s="16" t="n"/>
@@ -7195,7 +7195,7 @@
     <row r="318">
       <c r="A318" s="14" t="n"/>
       <c r="B318" s="15">
-        <f>IF($A318="","",TEXT($A318,"aaa"))</f>
+        <f>IF($A318="","",CHOOSE(WEEKDAY($A318),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C318" s="16" t="n"/>
@@ -7215,7 +7215,7 @@
     <row r="319">
       <c r="A319" s="14" t="n"/>
       <c r="B319" s="15">
-        <f>IF($A319="","",TEXT($A319,"aaa"))</f>
+        <f>IF($A319="","",CHOOSE(WEEKDAY($A319),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C319" s="16" t="n"/>
@@ -7235,7 +7235,7 @@
     <row r="320">
       <c r="A320" s="14" t="n"/>
       <c r="B320" s="15">
-        <f>IF($A320="","",TEXT($A320,"aaa"))</f>
+        <f>IF($A320="","",CHOOSE(WEEKDAY($A320),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C320" s="16" t="n"/>
@@ -7255,7 +7255,7 @@
     <row r="321">
       <c r="A321" s="14" t="n"/>
       <c r="B321" s="15">
-        <f>IF($A321="","",TEXT($A321,"aaa"))</f>
+        <f>IF($A321="","",CHOOSE(WEEKDAY($A321),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C321" s="16" t="n"/>
@@ -7275,7 +7275,7 @@
     <row r="322">
       <c r="A322" s="14" t="n"/>
       <c r="B322" s="15">
-        <f>IF($A322="","",TEXT($A322,"aaa"))</f>
+        <f>IF($A322="","",CHOOSE(WEEKDAY($A322),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C322" s="16" t="n"/>
@@ -7295,7 +7295,7 @@
     <row r="323">
       <c r="A323" s="14" t="n"/>
       <c r="B323" s="15">
-        <f>IF($A323="","",TEXT($A323,"aaa"))</f>
+        <f>IF($A323="","",CHOOSE(WEEKDAY($A323),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C323" s="16" t="n"/>
@@ -7315,7 +7315,7 @@
     <row r="324">
       <c r="A324" s="14" t="n"/>
       <c r="B324" s="15">
-        <f>IF($A324="","",TEXT($A324,"aaa"))</f>
+        <f>IF($A324="","",CHOOSE(WEEKDAY($A324),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C324" s="16" t="n"/>
@@ -7335,7 +7335,7 @@
     <row r="325">
       <c r="A325" s="14" t="n"/>
       <c r="B325" s="15">
-        <f>IF($A325="","",TEXT($A325,"aaa"))</f>
+        <f>IF($A325="","",CHOOSE(WEEKDAY($A325),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C325" s="16" t="n"/>
@@ -7355,7 +7355,7 @@
     <row r="326">
       <c r="A326" s="14" t="n"/>
       <c r="B326" s="15">
-        <f>IF($A326="","",TEXT($A326,"aaa"))</f>
+        <f>IF($A326="","",CHOOSE(WEEKDAY($A326),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C326" s="16" t="n"/>
@@ -7375,7 +7375,7 @@
     <row r="327">
       <c r="A327" s="14" t="n"/>
       <c r="B327" s="15">
-        <f>IF($A327="","",TEXT($A327,"aaa"))</f>
+        <f>IF($A327="","",CHOOSE(WEEKDAY($A327),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C327" s="16" t="n"/>
@@ -7395,7 +7395,7 @@
     <row r="328">
       <c r="A328" s="14" t="n"/>
       <c r="B328" s="15">
-        <f>IF($A328="","",TEXT($A328,"aaa"))</f>
+        <f>IF($A328="","",CHOOSE(WEEKDAY($A328),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C328" s="16" t="n"/>
@@ -7415,7 +7415,7 @@
     <row r="329">
       <c r="A329" s="14" t="n"/>
       <c r="B329" s="15">
-        <f>IF($A329="","",TEXT($A329,"aaa"))</f>
+        <f>IF($A329="","",CHOOSE(WEEKDAY($A329),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C329" s="16" t="n"/>
@@ -7435,7 +7435,7 @@
     <row r="330">
       <c r="A330" s="14" t="n"/>
       <c r="B330" s="15">
-        <f>IF($A330="","",TEXT($A330,"aaa"))</f>
+        <f>IF($A330="","",CHOOSE(WEEKDAY($A330),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C330" s="16" t="n"/>
@@ -7455,7 +7455,7 @@
     <row r="331">
       <c r="A331" s="14" t="n"/>
       <c r="B331" s="15">
-        <f>IF($A331="","",TEXT($A331,"aaa"))</f>
+        <f>IF($A331="","",CHOOSE(WEEKDAY($A331),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C331" s="16" t="n"/>
@@ -7475,7 +7475,7 @@
     <row r="332">
       <c r="A332" s="14" t="n"/>
       <c r="B332" s="15">
-        <f>IF($A332="","",TEXT($A332,"aaa"))</f>
+        <f>IF($A332="","",CHOOSE(WEEKDAY($A332),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C332" s="16" t="n"/>
@@ -7495,7 +7495,7 @@
     <row r="333">
       <c r="A333" s="14" t="n"/>
       <c r="B333" s="15">
-        <f>IF($A333="","",TEXT($A333,"aaa"))</f>
+        <f>IF($A333="","",CHOOSE(WEEKDAY($A333),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C333" s="16" t="n"/>
@@ -7515,7 +7515,7 @@
     <row r="334">
       <c r="A334" s="14" t="n"/>
       <c r="B334" s="15">
-        <f>IF($A334="","",TEXT($A334,"aaa"))</f>
+        <f>IF($A334="","",CHOOSE(WEEKDAY($A334),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C334" s="16" t="n"/>
@@ -7535,7 +7535,7 @@
     <row r="335">
       <c r="A335" s="14" t="n"/>
       <c r="B335" s="15">
-        <f>IF($A335="","",TEXT($A335,"aaa"))</f>
+        <f>IF($A335="","",CHOOSE(WEEKDAY($A335),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C335" s="16" t="n"/>
@@ -7555,7 +7555,7 @@
     <row r="336">
       <c r="A336" s="14" t="n"/>
       <c r="B336" s="15">
-        <f>IF($A336="","",TEXT($A336,"aaa"))</f>
+        <f>IF($A336="","",CHOOSE(WEEKDAY($A336),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C336" s="16" t="n"/>
@@ -7575,7 +7575,7 @@
     <row r="337">
       <c r="A337" s="14" t="n"/>
       <c r="B337" s="15">
-        <f>IF($A337="","",TEXT($A337,"aaa"))</f>
+        <f>IF($A337="","",CHOOSE(WEEKDAY($A337),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C337" s="16" t="n"/>
@@ -7595,7 +7595,7 @@
     <row r="338">
       <c r="A338" s="14" t="n"/>
       <c r="B338" s="15">
-        <f>IF($A338="","",TEXT($A338,"aaa"))</f>
+        <f>IF($A338="","",CHOOSE(WEEKDAY($A338),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C338" s="16" t="n"/>
@@ -7615,7 +7615,7 @@
     <row r="339">
       <c r="A339" s="14" t="n"/>
       <c r="B339" s="15">
-        <f>IF($A339="","",TEXT($A339,"aaa"))</f>
+        <f>IF($A339="","",CHOOSE(WEEKDAY($A339),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C339" s="16" t="n"/>
@@ -7635,7 +7635,7 @@
     <row r="340">
       <c r="A340" s="14" t="n"/>
       <c r="B340" s="15">
-        <f>IF($A340="","",TEXT($A340,"aaa"))</f>
+        <f>IF($A340="","",CHOOSE(WEEKDAY($A340),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C340" s="16" t="n"/>
@@ -7655,7 +7655,7 @@
     <row r="341">
       <c r="A341" s="14" t="n"/>
       <c r="B341" s="15">
-        <f>IF($A341="","",TEXT($A341,"aaa"))</f>
+        <f>IF($A341="","",CHOOSE(WEEKDAY($A341),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C341" s="16" t="n"/>
@@ -7675,7 +7675,7 @@
     <row r="342">
       <c r="A342" s="14" t="n"/>
       <c r="B342" s="15">
-        <f>IF($A342="","",TEXT($A342,"aaa"))</f>
+        <f>IF($A342="","",CHOOSE(WEEKDAY($A342),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C342" s="16" t="n"/>
@@ -7695,7 +7695,7 @@
     <row r="343">
       <c r="A343" s="14" t="n"/>
       <c r="B343" s="15">
-        <f>IF($A343="","",TEXT($A343,"aaa"))</f>
+        <f>IF($A343="","",CHOOSE(WEEKDAY($A343),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C343" s="16" t="n"/>
@@ -7715,7 +7715,7 @@
     <row r="344">
       <c r="A344" s="14" t="n"/>
       <c r="B344" s="15">
-        <f>IF($A344="","",TEXT($A344,"aaa"))</f>
+        <f>IF($A344="","",CHOOSE(WEEKDAY($A344),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C344" s="16" t="n"/>
@@ -7735,7 +7735,7 @@
     <row r="345">
       <c r="A345" s="14" t="n"/>
       <c r="B345" s="15">
-        <f>IF($A345="","",TEXT($A345,"aaa"))</f>
+        <f>IF($A345="","",CHOOSE(WEEKDAY($A345),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C345" s="16" t="n"/>
@@ -7755,7 +7755,7 @@
     <row r="346">
       <c r="A346" s="14" t="n"/>
       <c r="B346" s="15">
-        <f>IF($A346="","",TEXT($A346,"aaa"))</f>
+        <f>IF($A346="","",CHOOSE(WEEKDAY($A346),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C346" s="16" t="n"/>
@@ -7775,7 +7775,7 @@
     <row r="347">
       <c r="A347" s="14" t="n"/>
       <c r="B347" s="15">
-        <f>IF($A347="","",TEXT($A347,"aaa"))</f>
+        <f>IF($A347="","",CHOOSE(WEEKDAY($A347),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C347" s="16" t="n"/>
@@ -7795,7 +7795,7 @@
     <row r="348">
       <c r="A348" s="14" t="n"/>
       <c r="B348" s="15">
-        <f>IF($A348="","",TEXT($A348,"aaa"))</f>
+        <f>IF($A348="","",CHOOSE(WEEKDAY($A348),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C348" s="16" t="n"/>
@@ -7815,7 +7815,7 @@
     <row r="349">
       <c r="A349" s="14" t="n"/>
       <c r="B349" s="15">
-        <f>IF($A349="","",TEXT($A349,"aaa"))</f>
+        <f>IF($A349="","",CHOOSE(WEEKDAY($A349),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C349" s="16" t="n"/>
@@ -7835,7 +7835,7 @@
     <row r="350">
       <c r="A350" s="14" t="n"/>
       <c r="B350" s="15">
-        <f>IF($A350="","",TEXT($A350,"aaa"))</f>
+        <f>IF($A350="","",CHOOSE(WEEKDAY($A350),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C350" s="16" t="n"/>
@@ -7855,7 +7855,7 @@
     <row r="351">
       <c r="A351" s="14" t="n"/>
       <c r="B351" s="15">
-        <f>IF($A351="","",TEXT($A351,"aaa"))</f>
+        <f>IF($A351="","",CHOOSE(WEEKDAY($A351),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C351" s="16" t="n"/>
@@ -7875,7 +7875,7 @@
     <row r="352">
       <c r="A352" s="14" t="n"/>
       <c r="B352" s="15">
-        <f>IF($A352="","",TEXT($A352,"aaa"))</f>
+        <f>IF($A352="","",CHOOSE(WEEKDAY($A352),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C352" s="16" t="n"/>
@@ -7895,7 +7895,7 @@
     <row r="353">
       <c r="A353" s="14" t="n"/>
       <c r="B353" s="15">
-        <f>IF($A353="","",TEXT($A353,"aaa"))</f>
+        <f>IF($A353="","",CHOOSE(WEEKDAY($A353),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C353" s="16" t="n"/>
@@ -7915,7 +7915,7 @@
     <row r="354">
       <c r="A354" s="14" t="n"/>
       <c r="B354" s="15">
-        <f>IF($A354="","",TEXT($A354,"aaa"))</f>
+        <f>IF($A354="","",CHOOSE(WEEKDAY($A354),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C354" s="16" t="n"/>
@@ -7935,7 +7935,7 @@
     <row r="355">
       <c r="A355" s="14" t="n"/>
       <c r="B355" s="15">
-        <f>IF($A355="","",TEXT($A355,"aaa"))</f>
+        <f>IF($A355="","",CHOOSE(WEEKDAY($A355),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C355" s="16" t="n"/>
@@ -7955,7 +7955,7 @@
     <row r="356">
       <c r="A356" s="14" t="n"/>
       <c r="B356" s="15">
-        <f>IF($A356="","",TEXT($A356,"aaa"))</f>
+        <f>IF($A356="","",CHOOSE(WEEKDAY($A356),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C356" s="16" t="n"/>
@@ -7975,7 +7975,7 @@
     <row r="357">
       <c r="A357" s="14" t="n"/>
       <c r="B357" s="15">
-        <f>IF($A357="","",TEXT($A357,"aaa"))</f>
+        <f>IF($A357="","",CHOOSE(WEEKDAY($A357),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C357" s="16" t="n"/>
@@ -7995,7 +7995,7 @@
     <row r="358">
       <c r="A358" s="14" t="n"/>
       <c r="B358" s="15">
-        <f>IF($A358="","",TEXT($A358,"aaa"))</f>
+        <f>IF($A358="","",CHOOSE(WEEKDAY($A358),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C358" s="16" t="n"/>
@@ -8015,7 +8015,7 @@
     <row r="359">
       <c r="A359" s="14" t="n"/>
       <c r="B359" s="15">
-        <f>IF($A359="","",TEXT($A359,"aaa"))</f>
+        <f>IF($A359="","",CHOOSE(WEEKDAY($A359),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C359" s="16" t="n"/>
@@ -8035,7 +8035,7 @@
     <row r="360">
       <c r="A360" s="14" t="n"/>
       <c r="B360" s="15">
-        <f>IF($A360="","",TEXT($A360,"aaa"))</f>
+        <f>IF($A360="","",CHOOSE(WEEKDAY($A360),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C360" s="16" t="n"/>
@@ -8055,7 +8055,7 @@
     <row r="361">
       <c r="A361" s="14" t="n"/>
       <c r="B361" s="15">
-        <f>IF($A361="","",TEXT($A361,"aaa"))</f>
+        <f>IF($A361="","",CHOOSE(WEEKDAY($A361),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C361" s="16" t="n"/>
@@ -8075,7 +8075,7 @@
     <row r="362">
       <c r="A362" s="14" t="n"/>
       <c r="B362" s="15">
-        <f>IF($A362="","",TEXT($A362,"aaa"))</f>
+        <f>IF($A362="","",CHOOSE(WEEKDAY($A362),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C362" s="16" t="n"/>
@@ -8095,7 +8095,7 @@
     <row r="363">
       <c r="A363" s="14" t="n"/>
       <c r="B363" s="15">
-        <f>IF($A363="","",TEXT($A363,"aaa"))</f>
+        <f>IF($A363="","",CHOOSE(WEEKDAY($A363),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C363" s="16" t="n"/>
@@ -8115,7 +8115,7 @@
     <row r="364">
       <c r="A364" s="14" t="n"/>
       <c r="B364" s="15">
-        <f>IF($A364="","",TEXT($A364,"aaa"))</f>
+        <f>IF($A364="","",CHOOSE(WEEKDAY($A364),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C364" s="16" t="n"/>
@@ -8135,7 +8135,7 @@
     <row r="365">
       <c r="A365" s="14" t="n"/>
       <c r="B365" s="15">
-        <f>IF($A365="","",TEXT($A365,"aaa"))</f>
+        <f>IF($A365="","",CHOOSE(WEEKDAY($A365),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C365" s="16" t="n"/>
@@ -8155,7 +8155,7 @@
     <row r="366">
       <c r="A366" s="14" t="n"/>
       <c r="B366" s="15">
-        <f>IF($A366="","",TEXT($A366,"aaa"))</f>
+        <f>IF($A366="","",CHOOSE(WEEKDAY($A366),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C366" s="16" t="n"/>
@@ -8175,7 +8175,7 @@
     <row r="367">
       <c r="A367" s="14" t="n"/>
       <c r="B367" s="15">
-        <f>IF($A367="","",TEXT($A367,"aaa"))</f>
+        <f>IF($A367="","",CHOOSE(WEEKDAY($A367),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C367" s="16" t="n"/>
@@ -8195,7 +8195,7 @@
     <row r="368">
       <c r="A368" s="14" t="n"/>
       <c r="B368" s="15">
-        <f>IF($A368="","",TEXT($A368,"aaa"))</f>
+        <f>IF($A368="","",CHOOSE(WEEKDAY($A368),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C368" s="16" t="n"/>
@@ -8215,7 +8215,7 @@
     <row r="369">
       <c r="A369" s="14" t="n"/>
       <c r="B369" s="15">
-        <f>IF($A369="","",TEXT($A369,"aaa"))</f>
+        <f>IF($A369="","",CHOOSE(WEEKDAY($A369),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C369" s="16" t="n"/>
@@ -8235,7 +8235,7 @@
     <row r="370">
       <c r="A370" s="14" t="n"/>
       <c r="B370" s="15">
-        <f>IF($A370="","",TEXT($A370,"aaa"))</f>
+        <f>IF($A370="","",CHOOSE(WEEKDAY($A370),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C370" s="16" t="n"/>
@@ -8255,7 +8255,7 @@
     <row r="371">
       <c r="A371" s="14" t="n"/>
       <c r="B371" s="15">
-        <f>IF($A371="","",TEXT($A371,"aaa"))</f>
+        <f>IF($A371="","",CHOOSE(WEEKDAY($A371),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C371" s="16" t="n"/>
@@ -8275,7 +8275,7 @@
     <row r="372">
       <c r="A372" s="14" t="n"/>
       <c r="B372" s="15">
-        <f>IF($A372="","",TEXT($A372,"aaa"))</f>
+        <f>IF($A372="","",CHOOSE(WEEKDAY($A372),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C372" s="16" t="n"/>
@@ -8295,7 +8295,7 @@
     <row r="373">
       <c r="A373" s="14" t="n"/>
       <c r="B373" s="15">
-        <f>IF($A373="","",TEXT($A373,"aaa"))</f>
+        <f>IF($A373="","",CHOOSE(WEEKDAY($A373),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C373" s="16" t="n"/>
@@ -8315,7 +8315,7 @@
     <row r="374">
       <c r="A374" s="14" t="n"/>
       <c r="B374" s="15">
-        <f>IF($A374="","",TEXT($A374,"aaa"))</f>
+        <f>IF($A374="","",CHOOSE(WEEKDAY($A374),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C374" s="16" t="n"/>
@@ -8335,7 +8335,7 @@
     <row r="375">
       <c r="A375" s="14" t="n"/>
       <c r="B375" s="15">
-        <f>IF($A375="","",TEXT($A375,"aaa"))</f>
+        <f>IF($A375="","",CHOOSE(WEEKDAY($A375),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C375" s="16" t="n"/>
@@ -8355,7 +8355,7 @@
     <row r="376">
       <c r="A376" s="14" t="n"/>
       <c r="B376" s="15">
-        <f>IF($A376="","",TEXT($A376,"aaa"))</f>
+        <f>IF($A376="","",CHOOSE(WEEKDAY($A376),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C376" s="16" t="n"/>
@@ -8375,7 +8375,7 @@
     <row r="377">
       <c r="A377" s="14" t="n"/>
       <c r="B377" s="15">
-        <f>IF($A377="","",TEXT($A377,"aaa"))</f>
+        <f>IF($A377="","",CHOOSE(WEEKDAY($A377),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C377" s="16" t="n"/>
@@ -8395,7 +8395,7 @@
     <row r="378">
       <c r="A378" s="14" t="n"/>
       <c r="B378" s="15">
-        <f>IF($A378="","",TEXT($A378,"aaa"))</f>
+        <f>IF($A378="","",CHOOSE(WEEKDAY($A378),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C378" s="16" t="n"/>
@@ -8415,7 +8415,7 @@
     <row r="379">
       <c r="A379" s="14" t="n"/>
       <c r="B379" s="15">
-        <f>IF($A379="","",TEXT($A379,"aaa"))</f>
+        <f>IF($A379="","",CHOOSE(WEEKDAY($A379),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C379" s="16" t="n"/>
@@ -8435,7 +8435,7 @@
     <row r="380">
       <c r="A380" s="14" t="n"/>
       <c r="B380" s="15">
-        <f>IF($A380="","",TEXT($A380,"aaa"))</f>
+        <f>IF($A380="","",CHOOSE(WEEKDAY($A380),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C380" s="16" t="n"/>
@@ -8455,7 +8455,7 @@
     <row r="381">
       <c r="A381" s="14" t="n"/>
       <c r="B381" s="15">
-        <f>IF($A381="","",TEXT($A381,"aaa"))</f>
+        <f>IF($A381="","",CHOOSE(WEEKDAY($A381),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C381" s="16" t="n"/>
@@ -8475,7 +8475,7 @@
     <row r="382">
       <c r="A382" s="14" t="n"/>
       <c r="B382" s="15">
-        <f>IF($A382="","",TEXT($A382,"aaa"))</f>
+        <f>IF($A382="","",CHOOSE(WEEKDAY($A382),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C382" s="16" t="n"/>
@@ -8495,7 +8495,7 @@
     <row r="383">
       <c r="A383" s="14" t="n"/>
       <c r="B383" s="15">
-        <f>IF($A383="","",TEXT($A383,"aaa"))</f>
+        <f>IF($A383="","",CHOOSE(WEEKDAY($A383),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C383" s="16" t="n"/>
@@ -8515,7 +8515,7 @@
     <row r="384">
       <c r="A384" s="14" t="n"/>
       <c r="B384" s="15">
-        <f>IF($A384="","",TEXT($A384,"aaa"))</f>
+        <f>IF($A384="","",CHOOSE(WEEKDAY($A384),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C384" s="16" t="n"/>
@@ -8535,7 +8535,7 @@
     <row r="385">
       <c r="A385" s="14" t="n"/>
       <c r="B385" s="15">
-        <f>IF($A385="","",TEXT($A385,"aaa"))</f>
+        <f>IF($A385="","",CHOOSE(WEEKDAY($A385),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C385" s="16" t="n"/>
@@ -8555,7 +8555,7 @@
     <row r="386">
       <c r="A386" s="14" t="n"/>
       <c r="B386" s="15">
-        <f>IF($A386="","",TEXT($A386,"aaa"))</f>
+        <f>IF($A386="","",CHOOSE(WEEKDAY($A386),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C386" s="16" t="n"/>
@@ -8575,7 +8575,7 @@
     <row r="387">
       <c r="A387" s="14" t="n"/>
       <c r="B387" s="15">
-        <f>IF($A387="","",TEXT($A387,"aaa"))</f>
+        <f>IF($A387="","",CHOOSE(WEEKDAY($A387),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C387" s="16" t="n"/>
@@ -8595,7 +8595,7 @@
     <row r="388">
       <c r="A388" s="14" t="n"/>
       <c r="B388" s="15">
-        <f>IF($A388="","",TEXT($A388,"aaa"))</f>
+        <f>IF($A388="","",CHOOSE(WEEKDAY($A388),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C388" s="16" t="n"/>
@@ -8615,7 +8615,7 @@
     <row r="389">
       <c r="A389" s="14" t="n"/>
       <c r="B389" s="15">
-        <f>IF($A389="","",TEXT($A389,"aaa"))</f>
+        <f>IF($A389="","",CHOOSE(WEEKDAY($A389),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C389" s="16" t="n"/>
@@ -8635,7 +8635,7 @@
     <row r="390">
       <c r="A390" s="14" t="n"/>
       <c r="B390" s="15">
-        <f>IF($A390="","",TEXT($A390,"aaa"))</f>
+        <f>IF($A390="","",CHOOSE(WEEKDAY($A390),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C390" s="16" t="n"/>
@@ -8655,7 +8655,7 @@
     <row r="391">
       <c r="A391" s="14" t="n"/>
       <c r="B391" s="15">
-        <f>IF($A391="","",TEXT($A391,"aaa"))</f>
+        <f>IF($A391="","",CHOOSE(WEEKDAY($A391),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C391" s="16" t="n"/>
@@ -8675,7 +8675,7 @@
     <row r="392">
       <c r="A392" s="14" t="n"/>
       <c r="B392" s="15">
-        <f>IF($A392="","",TEXT($A392,"aaa"))</f>
+        <f>IF($A392="","",CHOOSE(WEEKDAY($A392),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C392" s="16" t="n"/>
@@ -8695,7 +8695,7 @@
     <row r="393">
       <c r="A393" s="14" t="n"/>
       <c r="B393" s="15">
-        <f>IF($A393="","",TEXT($A393,"aaa"))</f>
+        <f>IF($A393="","",CHOOSE(WEEKDAY($A393),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C393" s="16" t="n"/>
@@ -8715,7 +8715,7 @@
     <row r="394">
       <c r="A394" s="14" t="n"/>
       <c r="B394" s="15">
-        <f>IF($A394="","",TEXT($A394,"aaa"))</f>
+        <f>IF($A394="","",CHOOSE(WEEKDAY($A394),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C394" s="16" t="n"/>
@@ -8735,7 +8735,7 @@
     <row r="395">
       <c r="A395" s="14" t="n"/>
       <c r="B395" s="15">
-        <f>IF($A395="","",TEXT($A395,"aaa"))</f>
+        <f>IF($A395="","",CHOOSE(WEEKDAY($A395),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C395" s="16" t="n"/>
@@ -8755,7 +8755,7 @@
     <row r="396">
       <c r="A396" s="14" t="n"/>
       <c r="B396" s="15">
-        <f>IF($A396="","",TEXT($A396,"aaa"))</f>
+        <f>IF($A396="","",CHOOSE(WEEKDAY($A396),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C396" s="16" t="n"/>
@@ -8775,7 +8775,7 @@
     <row r="397">
       <c r="A397" s="14" t="n"/>
       <c r="B397" s="15">
-        <f>IF($A397="","",TEXT($A397,"aaa"))</f>
+        <f>IF($A397="","",CHOOSE(WEEKDAY($A397),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C397" s="16" t="n"/>
@@ -8795,7 +8795,7 @@
     <row r="398">
       <c r="A398" s="14" t="n"/>
       <c r="B398" s="15">
-        <f>IF($A398="","",TEXT($A398,"aaa"))</f>
+        <f>IF($A398="","",CHOOSE(WEEKDAY($A398),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C398" s="16" t="n"/>
@@ -8815,7 +8815,7 @@
     <row r="399">
       <c r="A399" s="14" t="n"/>
       <c r="B399" s="15">
-        <f>IF($A399="","",TEXT($A399,"aaa"))</f>
+        <f>IF($A399="","",CHOOSE(WEEKDAY($A399),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C399" s="16" t="n"/>
@@ -8835,7 +8835,7 @@
     <row r="400">
       <c r="A400" s="14" t="n"/>
       <c r="B400" s="15">
-        <f>IF($A400="","",TEXT($A400,"aaa"))</f>
+        <f>IF($A400="","",CHOOSE(WEEKDAY($A400),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C400" s="16" t="n"/>
@@ -8855,7 +8855,7 @@
     <row r="401">
       <c r="A401" s="14" t="n"/>
       <c r="B401" s="15">
-        <f>IF($A401="","",TEXT($A401,"aaa"))</f>
+        <f>IF($A401="","",CHOOSE(WEEKDAY($A401),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C401" s="16" t="n"/>
@@ -8875,7 +8875,7 @@
     <row r="402">
       <c r="A402" s="14" t="n"/>
       <c r="B402" s="15">
-        <f>IF($A402="","",TEXT($A402,"aaa"))</f>
+        <f>IF($A402="","",CHOOSE(WEEKDAY($A402),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C402" s="16" t="n"/>
@@ -8895,7 +8895,7 @@
     <row r="403">
       <c r="A403" s="14" t="n"/>
       <c r="B403" s="15">
-        <f>IF($A403="","",TEXT($A403,"aaa"))</f>
+        <f>IF($A403="","",CHOOSE(WEEKDAY($A403),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C403" s="16" t="n"/>
@@ -8915,7 +8915,7 @@
     <row r="404">
       <c r="A404" s="14" t="n"/>
       <c r="B404" s="15">
-        <f>IF($A404="","",TEXT($A404,"aaa"))</f>
+        <f>IF($A404="","",CHOOSE(WEEKDAY($A404),"日","月","火","水","木","金","土"))</f>
         <v/>
       </c>
       <c r="C404" s="16" t="n"/>
